--- a/Prediction Log.xlsx
+++ b/Prediction Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/109cad75520cd39f/Documents/Projects/Modelling/nrl-model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="11_F25DC773A252ABDACC1048EDD159412A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA14301-B9E4-42F6-971E-223369792B61}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="11_F25DC773A252ABDACC1048EDD159412A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976C05C1-EB7C-4DC1-A504-282EFB99FA76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,17 +349,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -416,54 +463,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="d/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -553,35 +552,35 @@
   </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{06A7AFB6-2725-4749-BA56-D9104726D73A}" uniqueName="1" name="match_id" queryTableFieldId="20"/>
-    <tableColumn id="4" xr3:uid="{EBBBD2A2-AEF1-40BC-8DE9-6AB25AEA9293}" uniqueName="4" name="date" queryTableFieldId="4" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{D601273A-8045-474A-9A33-40A47C431DD3}" uniqueName="2" name="home_team" queryTableFieldId="21" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{7580D706-9FB9-4514-8F94-0D9BF1581E19}" uniqueName="3" name="away_team" queryTableFieldId="22" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{EBBBD2A2-AEF1-40BC-8DE9-6AB25AEA9293}" uniqueName="4" name="date" queryTableFieldId="4" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{D601273A-8045-474A-9A33-40A47C431DD3}" uniqueName="2" name="home_team" queryTableFieldId="21" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{7580D706-9FB9-4514-8F94-0D9BF1581E19}" uniqueName="3" name="away_team" queryTableFieldId="22" dataDxfId="32"/>
     <tableColumn id="5" xr3:uid="{EF780FBE-D870-435A-92CE-5FD5E110230D}" uniqueName="5" name="home_prediction" queryTableFieldId="23"/>
     <tableColumn id="6" xr3:uid="{AE87FC99-393D-4BCE-B0A3-2EBB4C02A30D}" uniqueName="6" name="away_prediction" queryTableFieldId="24"/>
-    <tableColumn id="7" xr3:uid="{A40CBB36-AB06-43BA-86A3-5BB8A4F79197}" uniqueName="7" name="prediction" queryTableFieldId="25" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{CD595DA2-826E-4B90-84EC-FF3BD1890DB9}" uniqueName="8" name="commence_time" queryTableFieldId="26" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{A40CBB36-AB06-43BA-86A3-5BB8A4F79197}" uniqueName="7" name="prediction" queryTableFieldId="25" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{CD595DA2-826E-4B90-84EC-FF3BD1890DB9}" uniqueName="8" name="commence_time" queryTableFieldId="26" dataDxfId="30"/>
     <tableColumn id="9" xr3:uid="{7DA43A81-F48B-478C-B323-425968651CAD}" uniqueName="9" name="home_team_odds" queryTableFieldId="27"/>
     <tableColumn id="11" xr3:uid="{56876D7E-1D3C-4CE2-BBBB-4A517505BB9A}" uniqueName="11" name="away_team_odds" queryTableFieldId="28"/>
-    <tableColumn id="10" xr3:uid="{A9F6E55D-39DB-4383-AD5F-0F31607727CF}" uniqueName="10" name="bookmaker" queryTableFieldId="10" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{158FD286-E9BF-464A-BC3C-E9B8A589D134}" uniqueName="20" name="ev_bet" queryTableFieldId="29" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{BE994BCA-5DF9-492C-84E4-66BA1ABDF9ED}" uniqueName="15" name="Ev HomeAway" queryTableFieldId="14" dataDxfId="11">
+    <tableColumn id="10" xr3:uid="{A9F6E55D-39DB-4383-AD5F-0F31607727CF}" uniqueName="10" name="bookmaker" queryTableFieldId="10" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{158FD286-E9BF-464A-BC3C-E9B8A589D134}" uniqueName="20" name="ev_bet" queryTableFieldId="29" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{BE994BCA-5DF9-492C-84E4-66BA1ABDF9ED}" uniqueName="15" name="Ev HomeAway" queryTableFieldId="14" dataDxfId="27">
       <calculatedColumnFormula array="1">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0EF246E9-D782-4863-8A33-DA255226A82E}" uniqueName="16" name="Bet Line" queryTableFieldId="15" dataDxfId="10">
+    <tableColumn id="16" xr3:uid="{0EF246E9-D782-4863-8A33-DA255226A82E}" uniqueName="16" name="Bet Line" queryTableFieldId="15" dataDxfId="26">
       <calculatedColumnFormula array="1">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{0EE4036C-43AD-460A-82A3-CF7FF24C8174}" uniqueName="13" name="B365 Closing Line" queryTableFieldId="12" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{0EC28417-A937-484F-9FE1-42317BC57402}" uniqueName="14" name="CLV" queryTableFieldId="13" dataDxfId="8">
+    <tableColumn id="13" xr3:uid="{0EE4036C-43AD-460A-82A3-CF7FF24C8174}" uniqueName="13" name="B365 Closing Line" queryTableFieldId="12" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{0EC28417-A937-484F-9FE1-42317BC57402}" uniqueName="14" name="CLV" queryTableFieldId="13" dataDxfId="24">
       <calculatedColumnFormula>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{772F05D1-46FC-4FA4-B4B0-94EF906C734F}" uniqueName="18" name="Prediction HomeAway" queryTableFieldId="18" dataDxfId="7">
+    <tableColumn id="18" xr3:uid="{772F05D1-46FC-4FA4-B4B0-94EF906C734F}" uniqueName="18" name="Prediction HomeAway" queryTableFieldId="18" dataDxfId="23">
       <calculatedColumnFormula array="1">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{369B815A-F2EF-44EA-912E-DFE71912EE25}" uniqueName="12" name="Result HomeAway" queryTableFieldId="16" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{41A1C30B-F95C-486A-8BD2-EE905146F725}" uniqueName="19" name="Result Team" queryTableFieldId="19" dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{369B815A-F2EF-44EA-912E-DFE71912EE25}" uniqueName="12" name="Result HomeAway" queryTableFieldId="16" dataDxfId="22"/>
+    <tableColumn id="19" xr3:uid="{41A1C30B-F95C-486A-8BD2-EE905146F725}" uniqueName="19" name="Result Team" queryTableFieldId="19" dataDxfId="21">
       <calculatedColumnFormula array="1">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{F5AA482F-60CE-47E2-BA38-BEC8EBE5AD95}" uniqueName="17" name="Prediction Accuracy" queryTableFieldId="17" dataDxfId="4">
+    <tableColumn id="17" xr3:uid="{F5AA482F-60CE-47E2-BA38-BEC8EBE5AD95}" uniqueName="17" name="Prediction Accuracy" queryTableFieldId="17" dataDxfId="20">
       <calculatedColumnFormula>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -594,12 +593,12 @@
   <autoFilter ref="A1:G52" xr:uid="{EA0556F7-543C-4944-978D-945459AD5562}"/>
   <tableColumns count="7">
     <tableColumn id="3" xr3:uid="{34C834AF-3D03-4725-98AF-90E773DD7FAF}" uniqueName="3" name="match_id" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{2295DE2A-41B0-4CF1-892C-1083C94A72F9}" uniqueName="4" name="date" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{AAD13361-A670-4D79-935D-59B2B5E3ED9B}" uniqueName="6" name="home_team" queryTableFieldId="6" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{8A7BEB81-9F1E-4892-9BEE-CE6C90139899}" uniqueName="5" name="away_team" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{2295DE2A-41B0-4CF1-892C-1083C94A72F9}" uniqueName="4" name="date" queryTableFieldId="4" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{AAD13361-A670-4D79-935D-59B2B5E3ED9B}" uniqueName="6" name="home_team" queryTableFieldId="6" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{8A7BEB81-9F1E-4892-9BEE-CE6C90139899}" uniqueName="5" name="away_team" queryTableFieldId="5" dataDxfId="17"/>
     <tableColumn id="1" xr3:uid="{C7671F44-5AE9-4241-A406-9E873817137C}" uniqueName="1" name="home_prediction" queryTableFieldId="20"/>
     <tableColumn id="2" xr3:uid="{18D48C84-0C9C-47D7-BE93-72E1789651A0}" uniqueName="2" name="away_prediction" queryTableFieldId="21"/>
-    <tableColumn id="7" xr3:uid="{AB174EF5-B4ED-42BC-B2A7-8F8BA099EA18}" uniqueName="7" name="prediction" queryTableFieldId="22" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{AB174EF5-B4ED-42BC-B2A7-8F8BA099EA18}" uniqueName="7" name="prediction" queryTableFieldId="22" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -610,14 +609,14 @@
   <autoFilter ref="A1:I221" xr:uid="{E123EB28-4FAE-4F7E-8720-9105861DF85D}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8B526D9E-5D5A-44D3-93EF-AE9A17A97DDB}" uniqueName="1" name="match_id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{C8410AFE-BB42-45FC-825C-567BDB01273D}" uniqueName="2" name="commence_time" queryTableFieldId="9" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{71CC9BAC-72BA-4972-BF45-A0D2C7247690}" uniqueName="6" name="home_team" queryTableFieldId="6" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{6107C972-122F-4898-903F-60380DEA5474}" uniqueName="5" name="away_team" queryTableFieldId="5" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{8AB2C615-3EFF-47AD-8CEE-B71D5F38A190}" uniqueName="3" name="bookmaker" queryTableFieldId="3" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{78FC2688-610C-47E0-A269-FFD76B018E97}" uniqueName="7" name="market" queryTableFieldId="10" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{C8410AFE-BB42-45FC-825C-567BDB01273D}" uniqueName="2" name="commence_time" queryTableFieldId="9" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{71CC9BAC-72BA-4972-BF45-A0D2C7247690}" uniqueName="6" name="home_team" queryTableFieldId="6" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{6107C972-122F-4898-903F-60380DEA5474}" uniqueName="5" name="away_team" queryTableFieldId="5" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{8AB2C615-3EFF-47AD-8CEE-B71D5F38A190}" uniqueName="3" name="bookmaker" queryTableFieldId="3" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{78FC2688-610C-47E0-A269-FFD76B018E97}" uniqueName="7" name="market" queryTableFieldId="10" dataDxfId="11"/>
     <tableColumn id="8" xr3:uid="{49103BC7-DB7A-421F-ADB8-09906739D142}" uniqueName="8" name="home_team_odds" queryTableFieldId="11"/>
     <tableColumn id="9" xr3:uid="{164D5E29-FB0A-4EF9-8C8D-4916EE9707C3}" uniqueName="9" name="away_team_odds" queryTableFieldId="12"/>
-    <tableColumn id="4" xr3:uid="{BC9EF840-E8D3-475B-8FBF-0A4620CD2B85}" uniqueName="4" name="last_update" queryTableFieldId="4" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{BC9EF840-E8D3-475B-8FBF-0A4620CD2B85}" uniqueName="4" name="last_update" queryTableFieldId="4" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -628,13 +627,13 @@
   <autoFilter ref="A1:H89" xr:uid="{B3920497-7108-4423-B64B-C254CD0793EB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{F1482920-EC6D-4B71-9D9D-B62B2F8819B9}" name="match_id"/>
-    <tableColumn id="2" xr3:uid="{18F8765E-1EC8-4FD9-B491-FC165D62DCDA}" name="Date" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{3D7A90B9-B2B0-4C8A-970C-5F732C502C39}" name="Home Team" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{BBB57180-5B02-46A3-A7D5-51D9DD02582C}" name="Away Team" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{18F8765E-1EC8-4FD9-B491-FC165D62DCDA}" name="Date" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{3D7A90B9-B2B0-4C8A-970C-5F732C502C39}" name="Home Team" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{BBB57180-5B02-46A3-A7D5-51D9DD02582C}" name="Away Team" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{2CAC0C67-9A80-4110-AF3F-C33031059E27}" name="Home Odds"/>
     <tableColumn id="6" xr3:uid="{6B78A46B-75CD-4474-95D5-E9D6F1B376F0}" name="Away Odds"/>
-    <tableColumn id="7" xr3:uid="{162565F4-A769-4D6C-B194-6242AC8C8CE8}" name="Bookmaker" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{83C13F5A-7E41-4F96-8CCF-C24E006D5B4C}" name="Last Update" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{162565F4-A769-4D6C-B194-6242AC8C8CE8}" name="Bookmaker" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{83C13F5A-7E41-4F96-8CCF-C24E006D5B4C}" name="Last Update" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -645,13 +644,13 @@
   <autoFilter ref="A1:H9" xr:uid="{D0C12108-74D0-4B19-BDD4-D2B58C615EF0}"/>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{5F137923-4D13-420F-90B1-27D30D98E71F}" name="match_id"/>
-    <tableColumn id="3" xr3:uid="{4F1F9E81-6A9E-4CB0-BC6E-D18696EA4AC5}" name="date" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{0F4FCA7F-F413-4E4E-82A4-C16B4A1D3732}" name="home_team" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{C3A27DFA-71EF-47EC-B0D1-753ADB422FEE}" name="away_team" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{4F1F9E81-6A9E-4CB0-BC6E-D18696EA4AC5}" name="date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{0F4FCA7F-F413-4E4E-82A4-C16B4A1D3732}" name="home_team" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C3A27DFA-71EF-47EC-B0D1-753ADB422FEE}" name="away_team" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{D1ECF2A6-826D-491A-A765-18F4A065D68C}" name="home_odd"/>
     <tableColumn id="7" xr3:uid="{22B7621A-279A-4FF4-9EC0-4D529E83B8BF}" name="away_odd"/>
-    <tableColumn id="8" xr3:uid="{17F7CF52-A85D-46FA-8580-CB31383C5277}" name="bookmaker" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{ED7C4800-BB8D-4429-875C-46A948B2E040}" name="home_away" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{17F7CF52-A85D-46FA-8580-CB31383C5277}" name="bookmaker" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{ED7C4800-BB8D-4429-875C-46A948B2E040}" name="home_away" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1043,10 +1042,10 @@
       <c r="B2" s="2">
         <v>46135.416666666664</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2">
@@ -1055,33 +1054,30 @@
       <c r="F2">
         <v>0.53798824548721302</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="str" cm="1">
+      <c r="M2" t="str" cm="1">
         <f t="array" ref="M2">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N2" s="4" t="str" cm="1">
+      <c r="N2" t="str" cm="1">
         <f t="array" ref="N2">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="str">
+      <c r="P2" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q2" s="4" cm="1">
+      <c r="Q2" cm="1">
         <f t="array" ref="Q2">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2">
         <v>1</v>
       </c>
-      <c r="S2" s="4" t="str" cm="1">
+      <c r="S2" t="str" cm="1">
         <f t="array" ref="S2">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Tigers</v>
       </c>
@@ -1097,10 +1093,10 @@
       <c r="B3" s="2">
         <v>46136.416666666664</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3">
@@ -1109,33 +1105,30 @@
       <c r="F3">
         <v>0.55746001005172696</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="str" cm="1">
+      <c r="M3" t="str" cm="1">
         <f t="array" ref="M3">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N3" s="4" t="str" cm="1">
+      <c r="N3" t="str" cm="1">
         <f t="array" ref="N3">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4" t="str">
+      <c r="P3" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q3" s="4" cm="1">
+      <c r="Q3" cm="1">
         <f t="array" ref="Q3">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="S3" s="4" t="str" cm="1">
+      <c r="S3" t="str" cm="1">
         <f t="array" ref="S3">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Cowboys</v>
       </c>
@@ -1151,10 +1144,10 @@
       <c r="B4" s="2">
         <v>46136.416666666664</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4">
@@ -1163,33 +1156,30 @@
       <c r="F4">
         <v>0.51296186447143599</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="str" cm="1">
+      <c r="M4" t="str" cm="1">
         <f t="array" ref="M4">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N4" s="4" t="str" cm="1">
+      <c r="N4" t="str" cm="1">
         <f t="array" ref="N4">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4" t="str">
+      <c r="P4" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q4" s="4" cm="1">
+      <c r="Q4" cm="1">
         <f t="array" ref="Q4">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="4">
+      <c r="R4">
         <v>0</v>
       </c>
-      <c r="S4" s="4" t="str" cm="1">
+      <c r="S4" t="str" cm="1">
         <f t="array" ref="S4">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Bulldogs</v>
       </c>
@@ -1205,10 +1195,10 @@
       <c r="B5" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5">
@@ -1217,33 +1207,30 @@
       <c r="F5">
         <v>0.60073155164718595</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="str" cm="1">
+      <c r="M5" t="str" cm="1">
         <f t="array" ref="M5">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N5" s="4" t="str" cm="1">
+      <c r="N5" t="str" cm="1">
         <f t="array" ref="N5">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4" t="str">
+      <c r="P5" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q5" s="4" cm="1">
+      <c r="Q5" cm="1">
         <f t="array" ref="Q5">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R5" s="4">
+      <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="str" cm="1">
+      <c r="S5" t="str" cm="1">
         <f t="array" ref="S5">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Roosters</v>
       </c>
@@ -1259,10 +1246,10 @@
       <c r="B6" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6">
@@ -1271,33 +1258,30 @@
       <c r="F6">
         <v>0.310564994812012</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4" t="str" cm="1">
+      <c r="M6" t="str" cm="1">
         <f t="array" ref="M6">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N6" s="4" t="str" cm="1">
+      <c r="N6" t="str" cm="1">
         <f t="array" ref="N6">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4" t="str">
+      <c r="P6" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q6" s="4" cm="1">
+      <c r="Q6" cm="1">
         <f t="array" ref="Q6">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R6" s="4">
+      <c r="R6">
         <v>1</v>
       </c>
-      <c r="S6" s="4" t="str" cm="1">
+      <c r="S6" t="str" cm="1">
         <f t="array" ref="S6">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Warriors</v>
       </c>
@@ -1313,10 +1297,10 @@
       <c r="B7" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7">
@@ -1325,33 +1309,30 @@
       <c r="F7">
         <v>0.57372730970382702</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4" t="str" cm="1">
+      <c r="M7" t="str" cm="1">
         <f t="array" ref="M7">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N7" s="4" t="str" cm="1">
+      <c r="N7" t="str" cm="1">
         <f t="array" ref="N7">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4" t="str">
+      <c r="P7" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q7" s="4" cm="1">
+      <c r="Q7" cm="1">
         <f t="array" ref="Q7">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R7">
         <v>1</v>
       </c>
-      <c r="S7" s="4" t="str" cm="1">
+      <c r="S7" t="str" cm="1">
         <f t="array" ref="S7">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Storm</v>
       </c>
@@ -1367,10 +1348,10 @@
       <c r="B8" s="2">
         <v>46138.416666666664</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8">
@@ -1379,33 +1360,30 @@
       <c r="F8">
         <v>0.58672571182250999</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4" t="str" cm="1">
+      <c r="M8" t="str" cm="1">
         <f t="array" ref="M8">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N8" s="4" t="str" cm="1">
+      <c r="N8" t="str" cm="1">
         <f t="array" ref="N8">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4" t="str">
+      <c r="P8" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q8" s="4" cm="1">
+      <c r="Q8" cm="1">
         <f t="array" ref="Q8">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R8">
         <v>1</v>
       </c>
-      <c r="S8" s="4" t="str" cm="1">
+      <c r="S8" t="str" cm="1">
         <f t="array" ref="S8">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Knights</v>
       </c>
@@ -1421,10 +1399,10 @@
       <c r="B9" s="2">
         <v>46138.416666666664</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>18</v>
       </c>
       <c r="E9">
@@ -1433,33 +1411,30 @@
       <c r="F9">
         <v>0.48441731929779103</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4" t="str" cm="1">
+      <c r="M9" t="str" cm="1">
         <f t="array" ref="M9">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N9" s="4" t="str" cm="1">
+      <c r="N9" t="str" cm="1">
         <f t="array" ref="N9">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4" t="str">
+      <c r="P9" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q9" s="4" cm="1">
+      <c r="Q9" cm="1">
         <f t="array" ref="Q9">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9">
         <v>0</v>
       </c>
-      <c r="S9" s="4" t="str" cm="1">
+      <c r="S9" t="str" cm="1">
         <f t="array" ref="S9">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Eels</v>
       </c>
@@ -1475,10 +1450,10 @@
       <c r="B10" s="2">
         <v>46143.416666666664</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>7</v>
       </c>
       <c r="E10">
@@ -1487,33 +1462,30 @@
       <c r="F10">
         <v>0.56807678937911998</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>7</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4" t="str" cm="1">
+      <c r="M10" t="str" cm="1">
         <f t="array" ref="M10">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N10" s="4" t="str" cm="1">
+      <c r="N10" t="str" cm="1">
         <f t="array" ref="N10">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4" t="str">
+      <c r="P10" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q10" s="4" cm="1">
+      <c r="Q10" cm="1">
         <f t="array" ref="Q10">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R10" s="4">
+      <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10" s="4" t="str" cm="1">
+      <c r="S10" t="str" cm="1">
         <f t="array" ref="S10">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Cowboys</v>
       </c>
@@ -1529,10 +1501,10 @@
       <c r="B11" s="2">
         <v>46143.416666666664</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11">
@@ -1541,33 +1513,30 @@
       <c r="F11">
         <v>0.45479992032051098</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4" t="str" cm="1">
+      <c r="M11" t="str" cm="1">
         <f t="array" ref="M11">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N11" s="4" t="str" cm="1">
+      <c r="N11" t="str" cm="1">
         <f t="array" ref="N11">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4" t="str">
+      <c r="P11" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q11" s="4" cm="1">
+      <c r="Q11" cm="1">
         <f t="array" ref="Q11">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R11" s="4">
+      <c r="R11">
         <v>1</v>
       </c>
-      <c r="S11" s="4" t="str" cm="1">
+      <c r="S11" t="str" cm="1">
         <f t="array" ref="S11">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Dolphins</v>
       </c>
@@ -1583,10 +1552,10 @@
       <c r="B12" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12">
@@ -1595,33 +1564,30 @@
       <c r="F12">
         <v>0.53203493356704701</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4" t="str" cm="1">
+      <c r="M12" t="str" cm="1">
         <f t="array" ref="M12">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N12" s="4" t="str" cm="1">
+      <c r="N12" t="str" cm="1">
         <f t="array" ref="N12">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4" t="str">
+      <c r="P12" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q12" s="4" cm="1">
+      <c r="Q12" cm="1">
         <f t="array" ref="Q12">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R12">
         <v>1</v>
       </c>
-      <c r="S12" s="4" t="str" cm="1">
+      <c r="S12" t="str" cm="1">
         <f t="array" ref="S12">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Titans</v>
       </c>
@@ -1637,10 +1603,10 @@
       <c r="B13" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13">
@@ -1649,33 +1615,30 @@
       <c r="F13">
         <v>0.486856520175934</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4" t="str" cm="1">
+      <c r="M13" t="str" cm="1">
         <f t="array" ref="M13">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N13" s="4" t="str" cm="1">
+      <c r="N13" t="str" cm="1">
         <f t="array" ref="N13">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4" t="str">
+      <c r="P13" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q13" s="4" cm="1">
+      <c r="Q13" cm="1">
         <f t="array" ref="Q13">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R13" s="4">
+      <c r="R13">
         <v>1</v>
       </c>
-      <c r="S13" s="4" t="str" cm="1">
+      <c r="S13" t="str" cm="1">
         <f t="array" ref="S13">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Eels</v>
       </c>
@@ -1691,10 +1654,10 @@
       <c r="B14" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" t="s">
         <v>9</v>
       </c>
       <c r="E14">
@@ -1703,33 +1666,30 @@
       <c r="F14">
         <v>0.59157890081405595</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" t="s">
         <v>9</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4" t="str" cm="1">
+      <c r="M14" t="str" cm="1">
         <f t="array" ref="M14">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N14" s="4" t="str" cm="1">
+      <c r="N14" t="str" cm="1">
         <f t="array" ref="N14">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4" t="str">
+      <c r="P14" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q14" s="4" cm="1">
+      <c r="Q14" cm="1">
         <f t="array" ref="Q14">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R14">
         <v>1</v>
       </c>
-      <c r="S14" s="4" t="str" cm="1">
+      <c r="S14" t="str" cm="1">
         <f t="array" ref="S14">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Roosters</v>
       </c>
@@ -1745,10 +1705,10 @@
       <c r="B15" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="E15">
@@ -1757,33 +1717,30 @@
       <c r="F15">
         <v>0.50741475820541404</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4" t="str" cm="1">
+      <c r="M15" t="str" cm="1">
         <f t="array" ref="M15">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N15" s="4" t="str" cm="1">
+      <c r="N15" t="str" cm="1">
         <f t="array" ref="N15">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4" t="str">
+      <c r="P15" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q15" s="4" cm="1">
+      <c r="Q15" cm="1">
         <f t="array" ref="Q15">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="4">
+      <c r="R15">
         <v>1</v>
       </c>
-      <c r="S15" s="4" t="str" cm="1">
+      <c r="S15" t="str" cm="1">
         <f t="array" ref="S15">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Knights</v>
       </c>
@@ -1799,10 +1756,10 @@
       <c r="B16" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16">
@@ -1811,33 +1768,30 @@
       <c r="F16">
         <v>0.47291478514671298</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" t="s">
         <v>6</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4" t="str" cm="1">
+      <c r="M16" t="str" cm="1">
         <f t="array" ref="M16">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N16" s="4" t="str" cm="1">
+      <c r="N16" t="str" cm="1">
         <f t="array" ref="N16">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4" t="str">
+      <c r="P16" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q16" s="4" cm="1">
+      <c r="Q16" cm="1">
         <f t="array" ref="Q16">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R16" s="4">
+      <c r="R16">
         <v>0</v>
       </c>
-      <c r="S16" s="4" t="str" cm="1">
+      <c r="S16" t="str" cm="1">
         <f t="array" ref="S16">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Tigers</v>
       </c>
@@ -1853,10 +1807,10 @@
       <c r="B17" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17">
@@ -1865,33 +1819,30 @@
       <c r="F17">
         <v>0.51173377037048295</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4" t="str" cm="1">
+      <c r="M17" t="str" cm="1">
         <f t="array" ref="M17">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N17" s="4" t="str" cm="1">
+      <c r="N17" t="str" cm="1">
         <f t="array" ref="N17">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4" t="str">
+      <c r="P17" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q17" s="4" cm="1">
+      <c r="Q17" cm="1">
         <f t="array" ref="Q17">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="4">
+      <c r="R17">
         <v>1</v>
       </c>
-      <c r="S17" s="4" t="str" cm="1">
+      <c r="S17" t="str" cm="1">
         <f t="array" ref="S17">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Panthers</v>
       </c>
@@ -1907,10 +1858,10 @@
       <c r="B18" s="2">
         <v>46149.416666666664</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18">
@@ -1919,33 +1870,30 @@
       <c r="F18">
         <v>0.48925295472145103</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4" t="str" cm="1">
+      <c r="M18" t="str" cm="1">
         <f t="array" ref="M18">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N18" s="4" t="str" cm="1">
+      <c r="N18" t="str" cm="1">
         <f t="array" ref="N18">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4" t="str">
+      <c r="P18" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q18" s="4" cm="1">
+      <c r="Q18" cm="1">
         <f t="array" ref="Q18">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R18" s="4">
+      <c r="R18">
         <v>0</v>
       </c>
-      <c r="S18" s="4" t="str" cm="1">
+      <c r="S18" t="str" cm="1">
         <f t="array" ref="S18">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Bulldogs</v>
       </c>
@@ -1961,10 +1909,10 @@
       <c r="B19" s="2">
         <v>46150.416666666664</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19">
@@ -1973,33 +1921,30 @@
       <c r="F19">
         <v>0.37709304690361001</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4" t="str" cm="1">
+      <c r="M19" t="str" cm="1">
         <f t="array" ref="M19">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N19" s="4" t="str" cm="1">
+      <c r="N19" t="str" cm="1">
         <f t="array" ref="N19">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4" t="str">
+      <c r="P19" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q19" s="4" cm="1">
+      <c r="Q19" cm="1">
         <f t="array" ref="Q19">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R19" s="4">
+      <c r="R19">
         <v>1</v>
       </c>
-      <c r="S19" s="4" t="str" cm="1">
+      <c r="S19" t="str" cm="1">
         <f t="array" ref="S19">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Roosters</v>
       </c>
@@ -2015,10 +1960,10 @@
       <c r="B20" s="2">
         <v>46150.416666666664</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20">
@@ -2027,33 +1972,30 @@
       <c r="F20">
         <v>0.52485394477844205</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4" t="str" cm="1">
+      <c r="M20" t="str" cm="1">
         <f t="array" ref="M20">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N20" s="4" t="str" cm="1">
+      <c r="N20" t="str" cm="1">
         <f t="array" ref="N20">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4" t="str">
+      <c r="P20" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q20" s="4" cm="1">
+      <c r="Q20" cm="1">
         <f t="array" ref="Q20">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R20" s="4">
+      <c r="R20">
         <v>0</v>
       </c>
-      <c r="S20" s="4" t="str" cm="1">
+      <c r="S20" t="str" cm="1">
         <f t="array" ref="S20">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Eels</v>
       </c>
@@ -2069,10 +2011,10 @@
       <c r="B21" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" t="s">
         <v>17</v>
       </c>
       <c r="E21">
@@ -2081,32 +2023,30 @@
       <c r="F21">
         <v>0.53755897283554099</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="2"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4" t="str" cm="1">
+      <c r="M21" t="str" cm="1">
         <f t="array" ref="M21">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N21" s="4" t="str" cm="1">
+      <c r="N21" t="str" cm="1">
         <f t="array" ref="N21">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="P21" s="4" t="str">
+      <c r="P21" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q21" s="4" cm="1">
+      <c r="Q21" cm="1">
         <f t="array" ref="Q21">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R21" s="4">
+      <c r="R21">
         <v>0</v>
       </c>
-      <c r="S21" s="4" t="str" cm="1">
+      <c r="S21" t="str" cm="1">
         <f t="array" ref="S21">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Knights</v>
       </c>
@@ -2122,10 +2062,10 @@
       <c r="B22" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" t="s">
         <v>6</v>
       </c>
       <c r="E22">
@@ -2134,32 +2074,30 @@
       <c r="F22">
         <v>0.46172070503234902</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="2"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4" t="str" cm="1">
+      <c r="M22" t="str" cm="1">
         <f t="array" ref="M22">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N22" s="4" t="str" cm="1">
+      <c r="N22" t="str" cm="1">
         <f t="array" ref="N22">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="P22" s="4" t="str">
+      <c r="P22" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q22" s="4" cm="1">
+      <c r="Q22" cm="1">
         <f t="array" ref="Q22">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R22" s="4">
+      <c r="R22">
         <v>1</v>
       </c>
-      <c r="S22" s="4" t="str" cm="1">
+      <c r="S22" t="str" cm="1">
         <f t="array" ref="S22">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Rabbitohs</v>
       </c>
@@ -2175,10 +2113,10 @@
       <c r="B23" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" t="s">
         <v>9</v>
       </c>
       <c r="E23">
@@ -2187,33 +2125,30 @@
       <c r="F23">
         <v>0.58551681041717496</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" t="s">
         <v>9</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4" t="str" cm="1">
+      <c r="M23" t="str" cm="1">
         <f t="array" ref="M23">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N23" s="4" t="str" cm="1">
+      <c r="N23" t="str" cm="1">
         <f t="array" ref="N23">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4" t="str">
+      <c r="P23" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q23" s="4" cm="1">
+      <c r="Q23" cm="1">
         <f t="array" ref="Q23">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="4">
+      <c r="R23">
         <v>1</v>
       </c>
-      <c r="S23" s="4" t="str" cm="1">
+      <c r="S23" t="str" cm="1">
         <f t="array" ref="S23">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Eagles</v>
       </c>
@@ -2229,10 +2164,10 @@
       <c r="B24" s="2">
         <v>46152.416666666664</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
@@ -2241,32 +2176,30 @@
       <c r="F24">
         <v>0.47524529695510898</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4" t="str" cm="1">
+      <c r="M24" t="str" cm="1">
         <f t="array" ref="M24">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N24" s="4" t="str" cm="1">
+      <c r="N24" t="str" cm="1">
         <f t="array" ref="N24">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="P24" s="4" t="str">
+      <c r="P24" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q24" s="4" cm="1">
+      <c r="Q24" cm="1">
         <f t="array" ref="Q24">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R24" s="4">
+      <c r="R24">
         <v>0</v>
       </c>
-      <c r="S24" s="4" t="str" cm="1">
+      <c r="S24" t="str" cm="1">
         <f t="array" ref="S24">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Tigers</v>
       </c>
@@ -2282,10 +2215,10 @@
       <c r="B25" s="2">
         <v>46152.416666666664</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" t="s">
         <v>16</v>
       </c>
       <c r="E25">
@@ -2294,32 +2227,30 @@
       <c r="F25">
         <v>0.50954049825668302</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4" t="str" cm="1">
+      <c r="M25" t="str" cm="1">
         <f t="array" ref="M25">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v/>
       </c>
-      <c r="N25" s="4" t="str" cm="1">
+      <c r="N25" t="str" cm="1">
         <f t="array" ref="N25">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v/>
       </c>
-      <c r="P25" s="4" t="str">
+      <c r="P25" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q25" s="4" cm="1">
+      <c r="Q25" cm="1">
         <f t="array" ref="Q25">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R25" s="4">
+      <c r="R25">
         <v>0</v>
       </c>
-      <c r="S25" s="4" t="str" cm="1">
+      <c r="S25" t="str" cm="1">
         <f t="array" ref="S25">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Panthers</v>
       </c>
@@ -2335,10 +2266,10 @@
       <c r="B26" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26">
@@ -2347,7 +2278,7 @@
       <c r="F26">
         <v>0.415506571531296</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" t="s">
         <v>6</v>
       </c>
       <c r="H26" s="2">
@@ -2359,35 +2290,35 @@
       <c r="J26">
         <v>2.67</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" t="s">
         <v>61</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="4" t="str" cm="1">
+      <c r="M26" t="str" cm="1">
         <f t="array" ref="M26">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N26" s="4" cm="1">
+      <c r="N26" cm="1">
         <f t="array" ref="N26">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.67</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O26">
         <v>2.6</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>2.6923076923076827E-2</v>
       </c>
-      <c r="Q26" s="4" cm="1">
+      <c r="Q26" cm="1">
         <f t="array" ref="Q26">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26">
         <v>1</v>
       </c>
-      <c r="S26" s="4" t="str" cm="1">
+      <c r="S26" t="str" cm="1">
         <f t="array" ref="S26">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Sharks</v>
       </c>
@@ -2403,10 +2334,10 @@
       <c r="B27" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27">
@@ -2415,7 +2346,7 @@
       <c r="F27">
         <v>0.42789554595947299</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27" s="2">
@@ -2427,41 +2358,41 @@
       <c r="J27">
         <v>1.77</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" t="s">
         <v>14</v>
       </c>
-      <c r="M27" s="4" t="str" cm="1">
+      <c r="M27" t="str" cm="1">
         <f t="array" ref="M27">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N27" s="4" cm="1">
+      <c r="N27" cm="1">
         <f t="array" ref="N27">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.0499999999999998</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O27">
         <v>2.15</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>-4.6511627906976827E-2</v>
       </c>
-      <c r="Q27" s="4" cm="1">
+      <c r="Q27" cm="1">
         <f t="array" ref="Q27">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R27" s="4">
-        <v>1</v>
-      </c>
-      <c r="S27" s="4" t="str" cm="1">
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27" t="str" cm="1">
         <f t="array" ref="S27">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
-        <v>Rabbitohs</v>
+        <v>Dolphins</v>
       </c>
       <c r="T27" s="3">
         <f>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -2471,10 +2402,10 @@
       <c r="B28" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" t="s">
         <v>19</v>
       </c>
       <c r="E28">
@@ -2483,7 +2414,7 @@
       <c r="F28">
         <v>0.52386361360549905</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" t="s">
         <v>19</v>
       </c>
       <c r="H28" s="2">
@@ -2495,35 +2426,35 @@
       <c r="J28">
         <v>1.28</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" t="s">
         <v>62</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" t="s">
         <v>5</v>
       </c>
-      <c r="M28" s="4" t="str" cm="1">
+      <c r="M28" t="str" cm="1">
         <f t="array" ref="M28">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N28" s="4" cm="1">
+      <c r="N28" cm="1">
         <f t="array" ref="N28">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>3.7</v>
       </c>
-      <c r="O28" s="4">
-        <v>4.75</v>
-      </c>
-      <c r="P28" s="4">
+      <c r="O28">
+        <v>3.6</v>
+      </c>
+      <c r="P28">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>-0.22105263157894728</v>
-      </c>
-      <c r="Q28" s="4" cm="1">
+        <v>2.7777777777777901E-2</v>
+      </c>
+      <c r="Q28" cm="1">
         <f t="array" ref="Q28">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R28" s="4">
+      <c r="R28">
         <v>0</v>
       </c>
-      <c r="S28" s="4" t="str" cm="1">
+      <c r="S28" t="str" cm="1">
         <f t="array" ref="S28">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Eagles</v>
       </c>
@@ -2539,10 +2470,10 @@
       <c r="B29" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29">
@@ -2551,7 +2482,7 @@
       <c r="F29">
         <v>0.47857335209846502</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="2">
@@ -2563,35 +2494,35 @@
       <c r="J29">
         <v>4.75</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" t="s">
         <v>63</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" t="s">
         <v>7</v>
       </c>
-      <c r="M29" s="4" t="str" cm="1">
+      <c r="M29" t="str" cm="1">
         <f t="array" ref="M29">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N29" s="4" cm="1">
+      <c r="N29" cm="1">
         <f t="array" ref="N29">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>4.75</v>
       </c>
-      <c r="O29" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="P29" s="4">
+      <c r="O29">
+        <v>4.75</v>
+      </c>
+      <c r="P29">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="Q29" s="4" cm="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" cm="1">
         <f t="array" ref="Q29">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R29" s="4">
+      <c r="R29">
         <v>0</v>
       </c>
-      <c r="S29" s="4" t="str" cm="1">
+      <c r="S29" t="str" cm="1">
         <f t="array" ref="S29">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Cowboys</v>
       </c>
@@ -2607,10 +2538,10 @@
       <c r="B30" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" t="s">
         <v>15</v>
       </c>
       <c r="E30">
@@ -2619,7 +2550,7 @@
       <c r="F30">
         <v>0.488582283258438</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" t="s">
         <v>18</v>
       </c>
       <c r="H30" s="2">
@@ -2631,35 +2562,35 @@
       <c r="J30">
         <v>1.37</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" t="s">
         <v>18</v>
       </c>
-      <c r="M30" s="4" t="str" cm="1">
+      <c r="M30" t="str" cm="1">
         <f t="array" ref="M30">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N30" s="4" cm="1">
+      <c r="N30" cm="1">
         <f t="array" ref="N30">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>3.14</v>
       </c>
-      <c r="O30" s="4">
+      <c r="O30">
         <v>3.2</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>-1.8750000000000044E-2</v>
       </c>
-      <c r="Q30" s="4" cm="1">
+      <c r="Q30" cm="1">
         <f t="array" ref="Q30">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R30" s="4">
+      <c r="R30">
         <v>0</v>
       </c>
-      <c r="S30" s="4" t="str" cm="1">
+      <c r="S30" t="str" cm="1">
         <f t="array" ref="S30">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Storm</v>
       </c>
@@ -2675,10 +2606,10 @@
       <c r="B31" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" t="s">
         <v>17</v>
       </c>
       <c r="E31">
@@ -2687,7 +2618,7 @@
       <c r="F31">
         <v>0.558799088001251</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" t="s">
         <v>17</v>
       </c>
       <c r="H31" s="2">
@@ -2699,41 +2630,41 @@
       <c r="J31">
         <v>1.04</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" t="s">
         <v>64</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="4" t="str" cm="1">
+      <c r="M31" t="str" cm="1">
         <f t="array" ref="M31">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N31" s="4" cm="1">
+      <c r="N31" cm="1">
         <f t="array" ref="N31">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>3.65</v>
       </c>
-      <c r="O31" s="4">
-        <v>15</v>
-      </c>
-      <c r="P31" s="4">
+      <c r="O31">
+        <v>2.9</v>
+      </c>
+      <c r="P31">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>-0.75666666666666671</v>
-      </c>
-      <c r="Q31" s="4" cm="1">
+        <v>0.25862068965517238</v>
+      </c>
+      <c r="Q31" cm="1">
         <f t="array" ref="Q31">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R31" s="4">
-        <v>1</v>
-      </c>
-      <c r="S31" s="4" t="str" cm="1">
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31" t="str" cm="1">
         <f t="array" ref="S31">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
-        <v>Titans</v>
+        <v>Knights</v>
       </c>
       <c r="T31" s="3">
         <f>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -2743,10 +2674,10 @@
       <c r="B32" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>9</v>
       </c>
       <c r="E32">
@@ -2755,7 +2686,7 @@
       <c r="F32">
         <v>0.63762801885604903</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="2">
@@ -2767,41 +2698,41 @@
       <c r="J32">
         <v>2.3199999999999998</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" t="s">
         <v>64</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L32" t="s">
         <v>9</v>
       </c>
-      <c r="M32" s="4" t="str" cm="1">
+      <c r="M32" t="str" cm="1">
         <f t="array" ref="M32">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N32" s="4" cm="1">
+      <c r="N32" cm="1">
         <f t="array" ref="N32">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.3199999999999998</v>
       </c>
-      <c r="O32" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="P32" s="4">
+      <c r="O32">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P32">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>-0.20000000000000007</v>
-      </c>
-      <c r="Q32" s="4" cm="1">
+        <v>5.4545454545454453E-2</v>
+      </c>
+      <c r="Q32" cm="1">
         <f t="array" ref="Q32">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R32" s="4">
-        <v>0</v>
-      </c>
-      <c r="S32" s="4" t="str" cm="1">
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32" t="str" cm="1">
         <f t="array" ref="S32">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
-        <v>Broncos</v>
+        <v>Warriors</v>
       </c>
       <c r="T32" s="3">
         <f>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -2811,10 +2742,10 @@
       <c r="B33" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" t="s">
         <v>11</v>
       </c>
       <c r="E33">
@@ -2823,7 +2754,7 @@
       <c r="F33">
         <v>0.459474116563797</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" t="s">
         <v>16</v>
       </c>
       <c r="H33" s="2">
@@ -2835,35 +2766,35 @@
       <c r="J33">
         <v>14.5</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" t="s">
         <v>64</v>
       </c>
-      <c r="L33" s="4" t="s">
+      <c r="L33" t="s">
         <v>11</v>
       </c>
-      <c r="M33" s="4" t="str" cm="1">
+      <c r="M33" t="str" cm="1">
         <f t="array" ref="M33">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N33" s="4" cm="1">
+      <c r="N33" cm="1">
         <f t="array" ref="N33">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>14.5</v>
       </c>
-      <c r="O33" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P33" s="4">
+      <c r="O33">
+        <v>15</v>
+      </c>
+      <c r="P33">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>5.5909090909090899</v>
-      </c>
-      <c r="Q33" s="4" cm="1">
+        <v>-3.3333333333333326E-2</v>
+      </c>
+      <c r="Q33" cm="1">
         <f t="array" ref="Q33">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33">
         <v>1</v>
       </c>
-      <c r="S33" s="4" t="str" cm="1">
+      <c r="S33" t="str" cm="1">
         <f t="array" ref="S33">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Panthers</v>
       </c>
@@ -2879,10 +2810,10 @@
       <c r="B34" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34">
@@ -2891,7 +2822,7 @@
       <c r="F34">
         <v>0.55189061164856001</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="2">
@@ -2903,35 +2834,35 @@
       <c r="J34">
         <v>1.9</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" t="s">
         <v>62</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" t="s">
         <v>12</v>
       </c>
-      <c r="M34" s="4" t="str" cm="1">
+      <c r="M34" t="str" cm="1">
         <f t="array" ref="M34">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N34" s="4" cm="1">
+      <c r="N34" cm="1">
         <f t="array" ref="N34">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>1.9</v>
       </c>
-      <c r="O34" s="4">
+      <c r="O34">
         <v>2.2000000000000002</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>-0.13636363636363646</v>
       </c>
-      <c r="Q34" s="4" cm="1">
+      <c r="Q34" cm="1">
         <f t="array" ref="Q34">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34">
         <v>0</v>
       </c>
-      <c r="S34" s="4" t="str" cm="1">
+      <c r="S34" t="str" cm="1">
         <f t="array" ref="S34">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Dolphins</v>
       </c>
@@ -2947,10 +2878,10 @@
       <c r="B35" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" t="s">
         <v>15</v>
       </c>
       <c r="E35">
@@ -2959,7 +2890,7 @@
       <c r="F35">
         <v>0.48833516240119901</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" t="s">
         <v>8</v>
       </c>
       <c r="H35" s="2">
@@ -2971,35 +2902,35 @@
       <c r="J35">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" t="s">
         <v>62</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L35" t="s">
         <v>15</v>
       </c>
-      <c r="M35" s="4" t="str" cm="1">
+      <c r="M35" t="str" cm="1">
         <f t="array" ref="M35">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N35" s="4" cm="1">
+      <c r="N35" cm="1">
         <f t="array" ref="N35">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="O35" s="4">
+      <c r="O35">
         <v>2.0499999999999998</v>
       </c>
-      <c r="P35" s="4">
+      <c r="P35">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>7.317073170731736E-2</v>
       </c>
-      <c r="Q35" s="4" cm="1">
+      <c r="Q35" cm="1">
         <f t="array" ref="Q35">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R35" s="4">
+      <c r="R35">
         <v>1</v>
       </c>
-      <c r="S35" s="4" t="str" cm="1">
+      <c r="S35" t="str" cm="1">
         <f t="array" ref="S35">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Bulldogs</v>
       </c>
@@ -3015,10 +2946,10 @@
       <c r="B36" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" t="s">
         <v>13</v>
       </c>
       <c r="E36">
@@ -3027,7 +2958,7 @@
       <c r="F36">
         <v>0.52707517147064198</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" t="s">
         <v>13</v>
       </c>
       <c r="H36" s="2">
@@ -3039,41 +2970,41 @@
       <c r="J36">
         <v>1.18</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" t="s">
         <v>65</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="L36" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="4" t="str" cm="1">
+      <c r="M36" t="str" cm="1">
         <f t="array" ref="M36">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N36" s="4" cm="1">
+      <c r="N36" cm="1">
         <f t="array" ref="N36">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>5</v>
       </c>
-      <c r="O36" s="4">
+      <c r="O36">
         <v>4</v>
       </c>
-      <c r="P36" s="4">
+      <c r="P36">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>0.25</v>
       </c>
-      <c r="Q36" s="4" cm="1">
+      <c r="Q36" cm="1">
         <f t="array" ref="Q36">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R36" s="4">
-        <v>1</v>
-      </c>
-      <c r="S36" s="4" t="str" cm="1">
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36" t="str" cm="1">
         <f t="array" ref="S36">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
-        <v>Dragons</v>
+        <v>Warriors</v>
       </c>
       <c r="T36" s="3">
         <f>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -3083,10 +3014,10 @@
       <c r="B37" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" t="s">
         <v>22</v>
       </c>
       <c r="E37">
@@ -3095,7 +3026,7 @@
       <c r="F37">
         <v>0.43188309669494601</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" t="s">
         <v>19</v>
       </c>
       <c r="H37" s="2">
@@ -3107,41 +3038,41 @@
       <c r="J37">
         <v>4.0999999999999996</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" t="s">
         <v>61</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="L37" t="s">
         <v>22</v>
       </c>
-      <c r="M37" s="4" t="str" cm="1">
+      <c r="M37" t="str" cm="1">
         <f t="array" ref="M37">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N37" s="4" cm="1">
+      <c r="N37" cm="1">
         <f t="array" ref="N37">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="O37" s="4">
+      <c r="O37">
         <v>4</v>
       </c>
-      <c r="P37" s="4">
+      <c r="P37">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v>2.4999999999999911E-2</v>
       </c>
-      <c r="Q37" s="4" cm="1">
+      <c r="Q37" cm="1">
         <f t="array" ref="Q37">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R37" s="4">
-        <v>0</v>
-      </c>
-      <c r="S37" s="4" t="str" cm="1">
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37" t="str" cm="1">
         <f t="array" ref="S37">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
-        <v>Titans</v>
+        <v>Eagles</v>
       </c>
       <c r="T37" s="3">
         <f>IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]="", "", IF(Fact_Betting_Table[[#This Row],[Result HomeAway]]=Fact_Betting_Table[[#This Row],[Prediction HomeAway]],1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -3151,10 +3082,10 @@
       <c r="B38" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38">
@@ -3163,7 +3094,7 @@
       <c r="F38">
         <v>0.51445639133453402</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" t="s">
         <v>14</v>
       </c>
       <c r="H38" s="2">
@@ -3175,35 +3106,35 @@
       <c r="J38">
         <v>2.35</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" t="s">
         <v>66</v>
       </c>
-      <c r="L38" s="4" t="s">
+      <c r="L38" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="4" t="str" cm="1">
+      <c r="M38" t="str" cm="1">
         <f t="array" ref="M38">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N38" s="4" cm="1">
+      <c r="N38" cm="1">
         <f t="array" ref="N38">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.35</v>
       </c>
-      <c r="O38" s="4">
-        <v>2.4</v>
-      </c>
-      <c r="P38" s="4">
+      <c r="O38">
+        <v>2.35</v>
+      </c>
+      <c r="P38">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
-        <v>-2.0833333333333259E-2</v>
-      </c>
-      <c r="Q38" s="4" cm="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" cm="1">
         <f t="array" ref="Q38">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>0</v>
       </c>
-      <c r="R38" s="4">
+      <c r="R38">
         <v>1</v>
       </c>
-      <c r="S38" s="4" t="str" cm="1">
+      <c r="S38" t="str" cm="1">
         <f t="array" ref="S38">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v>Cowboys</v>
       </c>
@@ -3219,10 +3150,10 @@
       <c r="B39" s="2">
         <v>46172.25</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" t="s">
         <v>19</v>
       </c>
       <c r="E39">
@@ -3231,7 +3162,7 @@
       <c r="F39">
         <v>0.3767792284488678</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" t="s">
         <v>6</v>
       </c>
       <c r="H39" s="2">
@@ -3243,31 +3174,29 @@
       <c r="J39">
         <v>1.95</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" t="s">
         <v>66</v>
       </c>
-      <c r="L39" s="4" t="s">
+      <c r="L39" t="s">
         <v>6</v>
       </c>
-      <c r="M39" s="4" t="str" cm="1">
+      <c r="M39" t="str" cm="1">
         <f t="array" ref="M39">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N39" s="4" cm="1">
+      <c r="N39" cm="1">
         <f t="array" ref="N39">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>1.85</v>
       </c>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4" t="str">
+      <c r="P39" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q39" s="4" cm="1">
+      <c r="Q39" cm="1">
         <f t="array" ref="Q39">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4" t="str" cm="1">
+      <c r="S39" t="str" cm="1">
         <f t="array" ref="S39">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3283,10 +3212,10 @@
       <c r="B40" s="2">
         <v>46173.041666666664</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" t="s">
         <v>18</v>
       </c>
       <c r="E40">
@@ -3295,7 +3224,7 @@
       <c r="F40">
         <v>0.40699440240859985</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="2">
@@ -3307,31 +3236,29 @@
       <c r="J40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" t="s">
         <v>61</v>
       </c>
-      <c r="L40" s="4" t="s">
+      <c r="L40" t="s">
         <v>18</v>
       </c>
-      <c r="M40" s="4" t="str" cm="1">
+      <c r="M40" t="str" cm="1">
         <f t="array" ref="M40">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N40" s="4" cm="1">
+      <c r="N40" cm="1">
         <f t="array" ref="N40">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4" t="str">
+      <c r="P40" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q40" s="4" cm="1">
+      <c r="Q40" cm="1">
         <f t="array" ref="Q40">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4" t="str" cm="1">
+      <c r="S40" t="str" cm="1">
         <f t="array" ref="S40">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3347,10 +3274,10 @@
       <c r="B41" s="2">
         <v>46173.145833333336</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" t="s">
         <v>8</v>
       </c>
       <c r="E41">
@@ -3359,7 +3286,7 @@
       <c r="F41">
         <v>0.37593924999237061</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" t="s">
         <v>5</v>
       </c>
       <c r="H41" s="2">
@@ -3371,31 +3298,29 @@
       <c r="J41">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" t="s">
         <v>62</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="L41" t="s">
         <v>5</v>
       </c>
-      <c r="M41" s="4" t="str" cm="1">
+      <c r="M41" t="str" cm="1">
         <f t="array" ref="M41">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N41" s="4" cm="1">
+      <c r="N41" cm="1">
         <f t="array" ref="N41">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>1.62</v>
       </c>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4" t="str">
+      <c r="P41" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q41" s="4" cm="1">
+      <c r="Q41" cm="1">
         <f t="array" ref="Q41">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4" t="str" cm="1">
+      <c r="S41" t="str" cm="1">
         <f t="array" ref="S41">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3411,10 +3336,10 @@
       <c r="B42" s="2">
         <v>46173.232638888891</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" t="s">
         <v>10</v>
       </c>
       <c r="E42">
@@ -3423,7 +3348,7 @@
       <c r="F42">
         <v>0.37703040242195129</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="2">
@@ -3435,31 +3360,29 @@
       <c r="J42">
         <v>1.01</v>
       </c>
-      <c r="K42" s="4" t="s">
+      <c r="K42" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="4" t="s">
+      <c r="L42" t="s">
         <v>15</v>
       </c>
-      <c r="M42" s="4" t="str" cm="1">
+      <c r="M42" t="str" cm="1">
         <f t="array" ref="M42">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N42" s="4" cm="1">
+      <c r="N42" cm="1">
         <f t="array" ref="N42">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.1800000000000002</v>
       </c>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4" t="str">
+      <c r="P42" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q42" s="4" cm="1">
+      <c r="Q42" cm="1">
         <f t="array" ref="Q42">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4" t="str" cm="1">
+      <c r="S42" t="str" cm="1">
         <f t="array" ref="S42">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3475,10 +3398,10 @@
       <c r="B43" s="2">
         <v>46174</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43">
@@ -3487,7 +3410,7 @@
       <c r="F43">
         <v>0.3727455735206604</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="2">
@@ -3499,31 +3422,29 @@
       <c r="J43">
         <v>6.8</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" t="s">
         <v>64</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L43" t="s">
         <v>11</v>
       </c>
-      <c r="M43" s="4" t="str" cm="1">
+      <c r="M43" t="str" cm="1">
         <f t="array" ref="M43">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N43" s="4" cm="1">
+      <c r="N43" cm="1">
         <f t="array" ref="N43">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>6.8</v>
       </c>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4" t="str">
+      <c r="P43" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q43" s="4" cm="1">
+      <c r="Q43" cm="1">
         <f t="array" ref="Q43">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4" t="str" cm="1">
+      <c r="S43" t="str" cm="1">
         <f t="array" ref="S43">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3539,10 +3460,10 @@
       <c r="B44" s="2">
         <v>46173.416666666664</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44">
@@ -3551,7 +3472,7 @@
       <c r="F44">
         <v>0.48071816563606301</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="2">
@@ -3563,31 +3484,29 @@
       <c r="J44">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="K44" t="s">
         <v>64</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L44" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="4" t="str" cm="1">
+      <c r="M44" t="str" cm="1">
         <f t="array" ref="M44">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Home</v>
       </c>
-      <c r="N44" s="4" cm="1">
+      <c r="N44" cm="1">
         <f t="array" ref="N44">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>1.74</v>
       </c>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4" t="str">
+      <c r="P44" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q44" s="4" cm="1">
+      <c r="Q44" cm="1">
         <f t="array" ref="Q44">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4" t="str" cm="1">
+      <c r="S44" t="str" cm="1">
         <f t="array" ref="S44">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3603,10 +3522,10 @@
       <c r="B45" s="2">
         <v>46174.177083333336</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" t="s">
         <v>13</v>
       </c>
       <c r="E45">
@@ -3615,7 +3534,7 @@
       <c r="F45">
         <v>0.46154454350471497</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" t="s">
         <v>16</v>
       </c>
       <c r="H45" s="2">
@@ -3627,29 +3546,29 @@
       <c r="J45">
         <v>2.4</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" t="s">
         <v>67</v>
       </c>
-      <c r="L45" s="4" t="s">
+      <c r="L45" t="s">
         <v>13</v>
       </c>
-      <c r="M45" s="4" t="str" cm="1">
+      <c r="M45" t="str" cm="1">
         <f t="array" ref="M45">_xlfn.IFS(Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[home_team]],"Home",Fact_Betting_Table[[#This Row],[ev_bet]]=Fact_Betting_Table[[#This Row],[away_team]],"Away",Fact_Betting_Table[[#This Row],[ev_bet]]="","")</f>
         <v>Away</v>
       </c>
-      <c r="N45" s="4" cm="1">
+      <c r="N45" cm="1">
         <f t="array" ref="N45">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Home",Fact_Betting_Table[[#This Row],[home_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="Away",Fact_Betting_Table[[#This Row],[away_team_odds]],Fact_Betting_Table[[#This Row],[Ev HomeAway]]="","")</f>
         <v>2.4</v>
       </c>
-      <c r="P45" s="4" t="str">
+      <c r="P45" t="str">
         <f>IF(Fact_Betting_Table[[#This Row],[B365 Closing Line]]="", "", Fact_Betting_Table[[#This Row],[Bet Line]]/Fact_Betting_Table[[#This Row],[B365 Closing Line]]-1)</f>
         <v/>
       </c>
-      <c r="Q45" s="4" cm="1">
+      <c r="Q45" cm="1">
         <f t="array" ref="Q45">_xlfn.IFS(Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[home_team]], 1, Fact_Betting_Table[[#This Row],[prediction]]=Fact_Betting_Table[[#This Row],[away_team]], 0)</f>
         <v>1</v>
       </c>
-      <c r="S45" s="4" t="str" cm="1">
+      <c r="S45" t="str" cm="1">
         <f t="array" ref="S45">_xlfn.IFS(Fact_Betting_Table[[#This Row],[Result HomeAway]]=1,Fact_Betting_Table[[#This Row],[home_team]],Fact_Betting_Table[[#This Row],[Result HomeAway]]="","",Fact_Betting_Table[[#This Row],[Result HomeAway]]=0,Fact_Betting_Table[[#This Row],[away_team]])</f>
         <v/>
       </c>
@@ -3714,10 +3633,10 @@
       <c r="B2" s="2">
         <v>46135.416666666664</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2">
@@ -3726,7 +3645,7 @@
       <c r="F2">
         <v>0.53798824548721302</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3737,10 +3656,10 @@
       <c r="B3" s="2">
         <v>46136.416666666664</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3">
@@ -3749,7 +3668,7 @@
       <c r="F3">
         <v>0.51296186447143599</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3760,10 +3679,10 @@
       <c r="B4" s="2">
         <v>46136.416666666664</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4">
@@ -3772,7 +3691,7 @@
       <c r="F4">
         <v>0.55746001005172696</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3783,10 +3702,10 @@
       <c r="B5" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5">
@@ -3795,7 +3714,7 @@
       <c r="F5">
         <v>0.310564994812012</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3806,10 +3725,10 @@
       <c r="B6" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6">
@@ -3818,7 +3737,7 @@
       <c r="F6">
         <v>0.57372730970382702</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3829,10 +3748,10 @@
       <c r="B7" s="2">
         <v>46137.416666666664</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7">
@@ -3841,7 +3760,7 @@
       <c r="F7">
         <v>0.60073155164718595</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3852,10 +3771,10 @@
       <c r="B8" s="2">
         <v>46138.416666666664</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>18</v>
       </c>
       <c r="E8">
@@ -3864,7 +3783,7 @@
       <c r="F8">
         <v>0.48441731929779103</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3875,10 +3794,10 @@
       <c r="B9" s="2">
         <v>46138.416666666664</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9">
@@ -3887,7 +3806,7 @@
       <c r="F9">
         <v>0.58672571182250999</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3898,10 +3817,10 @@
       <c r="B10" s="2">
         <v>46143.416666666664</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>7</v>
       </c>
       <c r="E10">
@@ -3910,7 +3829,7 @@
       <c r="F10">
         <v>0.56807678937911998</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3921,10 +3840,10 @@
       <c r="B11" s="2">
         <v>46143.416666666664</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11">
@@ -3933,7 +3852,7 @@
       <c r="F11">
         <v>0.45479992032051098</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3944,10 +3863,10 @@
       <c r="B12" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
@@ -3956,7 +3875,7 @@
       <c r="F12">
         <v>0.59157890081405595</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3967,10 +3886,10 @@
       <c r="B13" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13">
@@ -3979,7 +3898,7 @@
       <c r="F13">
         <v>0.53203493356704701</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3990,10 +3909,10 @@
       <c r="B14" s="2">
         <v>46144.416666666664</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14">
@@ -4002,7 +3921,7 @@
       <c r="F14">
         <v>0.486856520175934</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4013,10 +3932,10 @@
       <c r="B15" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15">
@@ -4025,7 +3944,7 @@
       <c r="F15">
         <v>0.51173377037048295</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4036,10 +3955,10 @@
       <c r="B16" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" t="s">
         <v>14</v>
       </c>
       <c r="E16">
@@ -4048,7 +3967,7 @@
       <c r="F16">
         <v>0.50741475820541404</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4059,10 +3978,10 @@
       <c r="B17" s="2">
         <v>46145.416666666664</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17">
@@ -4071,7 +3990,7 @@
       <c r="F17">
         <v>0.47291478514671298</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4082,10 +4001,10 @@
       <c r="B18" s="2">
         <v>46149.416666666664</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18">
@@ -4094,7 +4013,7 @@
       <c r="F18">
         <v>0.48925295472145103</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4105,10 +4024,10 @@
       <c r="B19" s="2">
         <v>46150.416666666664</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19">
@@ -4117,7 +4036,7 @@
       <c r="F19">
         <v>0.52485394477844205</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4128,10 +4047,10 @@
       <c r="B20" s="2">
         <v>46150.416666666664</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" t="s">
         <v>22</v>
       </c>
       <c r="E20">
@@ -4140,7 +4059,7 @@
       <c r="F20">
         <v>0.37709304690361001</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4151,10 +4070,10 @@
       <c r="B21" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" t="s">
         <v>9</v>
       </c>
       <c r="E21">
@@ -4163,7 +4082,7 @@
       <c r="F21">
         <v>0.58551681041717496</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4174,10 +4093,10 @@
       <c r="B22" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22">
@@ -4186,7 +4105,7 @@
       <c r="F22">
         <v>0.53755897283554099</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4197,10 +4116,10 @@
       <c r="B23" s="2">
         <v>46151.416666666664</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" t="s">
         <v>6</v>
       </c>
       <c r="E23">
@@ -4209,7 +4128,7 @@
       <c r="F23">
         <v>0.46172070503234902</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4220,10 +4139,10 @@
       <c r="B24" s="2">
         <v>46152.416666666664</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" t="s">
         <v>16</v>
       </c>
       <c r="E24">
@@ -4232,7 +4151,7 @@
       <c r="F24">
         <v>0.50954049825668302</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4243,10 +4162,10 @@
       <c r="B25" s="2">
         <v>46152.416666666664</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25">
@@ -4255,7 +4174,7 @@
       <c r="F25">
         <v>0.47524529695510898</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4266,10 +4185,10 @@
       <c r="B26" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26">
@@ -4278,7 +4197,7 @@
       <c r="F26">
         <v>0.415506571531296</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4289,10 +4208,10 @@
       <c r="B27" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27">
@@ -4301,7 +4220,7 @@
       <c r="F27">
         <v>0.42789554595947299</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4312,10 +4231,10 @@
       <c r="B28" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28">
@@ -4324,7 +4243,7 @@
       <c r="F28">
         <v>0.47857335209846502</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4335,10 +4254,10 @@
       <c r="B29" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" t="s">
         <v>19</v>
       </c>
       <c r="E29">
@@ -4347,7 +4266,7 @@
       <c r="F29">
         <v>0.52386361360549905</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4358,10 +4277,10 @@
       <c r="B30" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" t="s">
         <v>15</v>
       </c>
       <c r="E30">
@@ -4370,7 +4289,7 @@
       <c r="F30">
         <v>0.488582283258438</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4381,10 +4300,10 @@
       <c r="B31" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" t="s">
         <v>9</v>
       </c>
       <c r="E31">
@@ -4393,7 +4312,7 @@
       <c r="F31">
         <v>0.63762801885604903</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4404,10 +4323,10 @@
       <c r="B32" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32">
@@ -4416,7 +4335,7 @@
       <c r="F32">
         <v>0.459474116563797</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4427,10 +4346,10 @@
       <c r="B33" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="E33">
@@ -4439,7 +4358,7 @@
       <c r="F33">
         <v>0.558799088001251</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4450,10 +4369,10 @@
       <c r="B34" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34">
@@ -4462,7 +4381,7 @@
       <c r="F34">
         <v>0.55189061164856001</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4473,10 +4392,10 @@
       <c r="B35" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" t="s">
         <v>15</v>
       </c>
       <c r="E35">
@@ -4485,7 +4404,7 @@
       <c r="F35">
         <v>0.48833516240119901</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4496,10 +4415,10 @@
       <c r="B36" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" t="s">
         <v>22</v>
       </c>
       <c r="E36">
@@ -4508,7 +4427,7 @@
       <c r="F36">
         <v>0.43188309669494601</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4519,10 +4438,10 @@
       <c r="B37" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" t="s">
         <v>13</v>
       </c>
       <c r="E37">
@@ -4531,7 +4450,7 @@
       <c r="F37">
         <v>0.52707517147064198</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4542,10 +4461,10 @@
       <c r="B38" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38">
@@ -4554,7 +4473,7 @@
       <c r="F38">
         <v>0.51445639133453402</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4565,10 +4484,10 @@
       <c r="B39" s="2">
         <v>46171.416666666664</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" t="s">
         <v>19</v>
       </c>
       <c r="E39">
@@ -4577,7 +4496,7 @@
       <c r="F39">
         <v>0.43153256177902199</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4588,10 +4507,10 @@
       <c r="B40" s="2">
         <v>46172.416666666664</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" t="s">
         <v>18</v>
       </c>
       <c r="E40">
@@ -4600,7 +4519,7 @@
       <c r="F40">
         <v>0.62984424829482999</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4611,10 +4530,10 @@
       <c r="B41" s="2">
         <v>46172.416666666664</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" t="s">
         <v>8</v>
       </c>
       <c r="E41">
@@ -4623,7 +4542,7 @@
       <c r="F41">
         <v>0.51189380884170499</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4634,10 +4553,10 @@
       <c r="B42" s="2">
         <v>46172.416666666664</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" t="s">
         <v>10</v>
       </c>
       <c r="E42">
@@ -4646,7 +4565,7 @@
       <c r="F42">
         <v>0.49426224827766402</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4657,10 +4576,10 @@
       <c r="B43" s="2">
         <v>46173.416666666664</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43">
@@ -4669,7 +4588,7 @@
       <c r="F43">
         <v>0.45958527922630299</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4680,10 +4599,10 @@
       <c r="B44" s="2">
         <v>46173.416666666664</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44">
@@ -4692,7 +4611,7 @@
       <c r="F44">
         <v>0.48071816563606301</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4703,10 +4622,10 @@
       <c r="B45" s="2">
         <v>46173.416666666664</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" t="s">
         <v>13</v>
       </c>
       <c r="E45">
@@ -4715,7 +4634,7 @@
       <c r="F45">
         <v>0.51590502262115501</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4726,10 +4645,10 @@
       <c r="B46" s="2">
         <v>46172.25</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" t="s">
         <v>19</v>
       </c>
       <c r="E46">
@@ -4738,7 +4657,7 @@
       <c r="F46">
         <v>0.3767792284488678</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4749,10 +4668,10 @@
       <c r="B47" s="2">
         <v>46173.041666666664</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47">
@@ -4761,7 +4680,7 @@
       <c r="F47">
         <v>0.40699440240859985</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4772,10 +4691,10 @@
       <c r="B48" s="2">
         <v>46173.145833333336</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" t="s">
         <v>8</v>
       </c>
       <c r="E48">
@@ -4784,7 +4703,7 @@
       <c r="F48">
         <v>0.37593924999237061</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4795,10 +4714,10 @@
       <c r="B49" s="2">
         <v>46173.232638888891</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" t="s">
         <v>10</v>
       </c>
       <c r="E49">
@@ -4807,7 +4726,7 @@
       <c r="F49">
         <v>0.37703040242195129</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4818,10 +4737,10 @@
       <c r="B50" s="2">
         <v>46174</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="E50">
@@ -4830,7 +4749,7 @@
       <c r="F50">
         <v>0.3727455735206604</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4841,10 +4760,10 @@
       <c r="B51" s="2">
         <v>46174.086805555555</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" t="s">
         <v>7</v>
       </c>
       <c r="E51">
@@ -4853,7 +4772,7 @@
       <c r="F51">
         <v>0.37634444236755371</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4864,10 +4783,10 @@
       <c r="B52" s="2">
         <v>46174.177083333336</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" t="s">
         <v>13</v>
       </c>
       <c r="E52">
@@ -4876,7 +4795,7 @@
       <c r="F52">
         <v>0.46154454350471497</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4943,16 +4862,16 @@
       <c r="B2" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>69</v>
       </c>
       <c r="G2">
@@ -4972,16 +4891,16 @@
       <c r="B3" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>69</v>
       </c>
       <c r="G3">
@@ -5001,16 +4920,16 @@
       <c r="B4" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" t="s">
         <v>69</v>
       </c>
       <c r="G4">
@@ -5030,16 +4949,16 @@
       <c r="B5" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" t="s">
         <v>69</v>
       </c>
       <c r="G5">
@@ -5059,16 +4978,16 @@
       <c r="B6" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
         <v>69</v>
       </c>
       <c r="G6">
@@ -5088,16 +5007,16 @@
       <c r="B7" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" t="s">
         <v>69</v>
       </c>
       <c r="G7">
@@ -5117,16 +5036,16 @@
       <c r="B8" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" t="s">
         <v>69</v>
       </c>
       <c r="G8">
@@ -5146,16 +5065,16 @@
       <c r="B9" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" t="s">
         <v>69</v>
       </c>
       <c r="G9">
@@ -5175,16 +5094,16 @@
       <c r="B10" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" t="s">
         <v>69</v>
       </c>
       <c r="G10">
@@ -5204,16 +5123,16 @@
       <c r="B11" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" t="s">
         <v>69</v>
       </c>
       <c r="G11">
@@ -5233,16 +5152,16 @@
       <c r="B12" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" t="s">
         <v>69</v>
       </c>
       <c r="G12">
@@ -5262,16 +5181,16 @@
       <c r="B13" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" t="s">
         <v>69</v>
       </c>
       <c r="G13">
@@ -5291,16 +5210,16 @@
       <c r="B14" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" t="s">
         <v>69</v>
       </c>
       <c r="G14">
@@ -5320,16 +5239,16 @@
       <c r="B15" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" t="s">
         <v>69</v>
       </c>
       <c r="G15">
@@ -5349,16 +5268,16 @@
       <c r="B16" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" t="s">
         <v>69</v>
       </c>
       <c r="G16">
@@ -5378,16 +5297,16 @@
       <c r="B17" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" t="s">
         <v>69</v>
       </c>
       <c r="G17">
@@ -5407,16 +5326,16 @@
       <c r="B18" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" t="s">
         <v>69</v>
       </c>
       <c r="G18">
@@ -5436,16 +5355,16 @@
       <c r="B19" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" t="s">
         <v>69</v>
       </c>
       <c r="G19">
@@ -5465,16 +5384,16 @@
       <c r="B20" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" t="s">
         <v>69</v>
       </c>
       <c r="G20">
@@ -5494,16 +5413,16 @@
       <c r="B21" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" t="s">
         <v>69</v>
       </c>
       <c r="G21">
@@ -5523,16 +5442,16 @@
       <c r="B22" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" t="s">
         <v>69</v>
       </c>
       <c r="G22">
@@ -5552,16 +5471,16 @@
       <c r="B23" s="2">
         <v>46157.416666666664</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" t="s">
         <v>69</v>
       </c>
       <c r="G23">
@@ -5581,16 +5500,16 @@
       <c r="B24" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" t="s">
         <v>69</v>
       </c>
       <c r="G24">
@@ -5610,16 +5529,16 @@
       <c r="B25" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" t="s">
         <v>69</v>
       </c>
       <c r="G25">
@@ -5639,16 +5558,16 @@
       <c r="B26" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" t="s">
         <v>69</v>
       </c>
       <c r="G26">
@@ -5668,16 +5587,16 @@
       <c r="B27" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" t="s">
         <v>69</v>
       </c>
       <c r="G27">
@@ -5697,16 +5616,16 @@
       <c r="B28" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" t="s">
         <v>69</v>
       </c>
       <c r="G28">
@@ -5726,16 +5645,16 @@
       <c r="B29" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" t="s">
         <v>69</v>
       </c>
       <c r="G29">
@@ -5755,16 +5674,16 @@
       <c r="B30" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" t="s">
         <v>69</v>
       </c>
       <c r="G30">
@@ -5784,16 +5703,16 @@
       <c r="B31" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" t="s">
         <v>69</v>
       </c>
       <c r="G31">
@@ -5813,16 +5732,16 @@
       <c r="B32" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" t="s">
         <v>69</v>
       </c>
       <c r="G32">
@@ -5842,16 +5761,16 @@
       <c r="B33" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" t="s">
         <v>69</v>
       </c>
       <c r="G33">
@@ -5871,16 +5790,16 @@
       <c r="B34" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" t="s">
         <v>69</v>
       </c>
       <c r="G34">
@@ -5900,16 +5819,16 @@
       <c r="B35" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" t="s">
         <v>69</v>
       </c>
       <c r="G35">
@@ -5929,16 +5848,16 @@
       <c r="B36" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" t="s">
         <v>69</v>
       </c>
       <c r="G36">
@@ -5958,16 +5877,16 @@
       <c r="B37" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" t="s">
         <v>69</v>
       </c>
       <c r="G37">
@@ -5987,16 +5906,16 @@
       <c r="B38" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" t="s">
         <v>69</v>
       </c>
       <c r="G38">
@@ -6016,16 +5935,16 @@
       <c r="B39" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" t="s">
         <v>69</v>
       </c>
       <c r="G39">
@@ -6045,16 +5964,16 @@
       <c r="B40" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" t="s">
         <v>71</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" t="s">
         <v>69</v>
       </c>
       <c r="G40">
@@ -6074,16 +5993,16 @@
       <c r="B41" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" t="s">
         <v>69</v>
       </c>
       <c r="G41">
@@ -6103,16 +6022,16 @@
       <c r="B42" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" t="s">
         <v>69</v>
       </c>
       <c r="G42">
@@ -6132,16 +6051,16 @@
       <c r="B43" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" t="s">
         <v>69</v>
       </c>
       <c r="G43">
@@ -6161,16 +6080,16 @@
       <c r="B44" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" t="s">
         <v>72</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" t="s">
         <v>69</v>
       </c>
       <c r="G44">
@@ -6190,16 +6109,16 @@
       <c r="B45" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" t="s">
         <v>73</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" t="s">
         <v>69</v>
       </c>
       <c r="G45">
@@ -6219,16 +6138,16 @@
       <c r="B46" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" t="s">
         <v>69</v>
       </c>
       <c r="G46">
@@ -6248,16 +6167,16 @@
       <c r="B47" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" t="s">
         <v>69</v>
       </c>
       <c r="G47">
@@ -6277,16 +6196,16 @@
       <c r="B48" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" t="s">
         <v>66</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" t="s">
         <v>69</v>
       </c>
       <c r="G48">
@@ -6306,16 +6225,16 @@
       <c r="B49" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" t="s">
         <v>70</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" t="s">
         <v>69</v>
       </c>
       <c r="G49">
@@ -6335,16 +6254,16 @@
       <c r="B50" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" t="s">
         <v>69</v>
       </c>
       <c r="G50">
@@ -6364,16 +6283,16 @@
       <c r="B51" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" t="s">
         <v>71</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" t="s">
         <v>69</v>
       </c>
       <c r="G51">
@@ -6393,16 +6312,16 @@
       <c r="B52" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" t="s">
         <v>69</v>
       </c>
       <c r="G52">
@@ -6422,16 +6341,16 @@
       <c r="B53" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" t="s">
         <v>61</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" t="s">
         <v>69</v>
       </c>
       <c r="G53">
@@ -6451,16 +6370,16 @@
       <c r="B54" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" t="s">
         <v>69</v>
       </c>
       <c r="G54">
@@ -6480,16 +6399,16 @@
       <c r="B55" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" t="s">
         <v>15</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" t="s">
         <v>72</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" t="s">
         <v>69</v>
       </c>
       <c r="G55">
@@ -6509,16 +6428,16 @@
       <c r="B56" s="2">
         <v>46158.416666666664</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" t="s">
         <v>69</v>
       </c>
       <c r="G56">
@@ -6538,16 +6457,16 @@
       <c r="B57" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" t="s">
         <v>17</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" t="s">
         <v>63</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" t="s">
         <v>69</v>
       </c>
       <c r="G57">
@@ -6567,16 +6486,16 @@
       <c r="B58" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" t="s">
         <v>17</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" t="s">
         <v>64</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" t="s">
         <v>69</v>
       </c>
       <c r="G58">
@@ -6596,16 +6515,16 @@
       <c r="B59" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" t="s">
         <v>69</v>
       </c>
       <c r="G59">
@@ -6625,16 +6544,16 @@
       <c r="B60" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" t="s">
         <v>17</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" t="s">
         <v>70</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" t="s">
         <v>69</v>
       </c>
       <c r="G60">
@@ -6654,16 +6573,16 @@
       <c r="B61" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" t="s">
         <v>65</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" t="s">
         <v>69</v>
       </c>
       <c r="G61">
@@ -6683,16 +6602,16 @@
       <c r="B62" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" t="s">
         <v>17</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" t="s">
         <v>71</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" t="s">
         <v>69</v>
       </c>
       <c r="G62">
@@ -6712,16 +6631,16 @@
       <c r="B63" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" t="s">
         <v>17</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" t="s">
         <v>69</v>
       </c>
       <c r="G63">
@@ -6741,16 +6660,16 @@
       <c r="B64" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" t="s">
         <v>61</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" t="s">
         <v>69</v>
       </c>
       <c r="G64">
@@ -6770,16 +6689,16 @@
       <c r="B65" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" t="s">
         <v>17</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" t="s">
         <v>62</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" t="s">
         <v>69</v>
       </c>
       <c r="G65">
@@ -6799,16 +6718,16 @@
       <c r="B66" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" t="s">
         <v>72</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" t="s">
         <v>69</v>
       </c>
       <c r="G66">
@@ -6828,16 +6747,16 @@
       <c r="B67" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" t="s">
         <v>69</v>
       </c>
       <c r="G67">
@@ -6857,16 +6776,16 @@
       <c r="B68" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" t="s">
         <v>69</v>
       </c>
       <c r="G68">
@@ -6886,16 +6805,16 @@
       <c r="B69" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" t="s">
         <v>13</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" t="s">
         <v>64</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" t="s">
         <v>69</v>
       </c>
       <c r="G69">
@@ -6915,16 +6834,16 @@
       <c r="B70" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" t="s">
         <v>66</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" t="s">
         <v>69</v>
       </c>
       <c r="G70">
@@ -6944,16 +6863,16 @@
       <c r="B71" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" t="s">
         <v>70</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" t="s">
         <v>69</v>
       </c>
       <c r="G71">
@@ -6973,16 +6892,16 @@
       <c r="B72" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" t="s">
         <v>65</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" t="s">
         <v>69</v>
       </c>
       <c r="G72">
@@ -7002,16 +6921,16 @@
       <c r="B73" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" t="s">
         <v>13</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" t="s">
         <v>71</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" t="s">
         <v>69</v>
       </c>
       <c r="G73">
@@ -7031,16 +6950,16 @@
       <c r="B74" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" t="s">
         <v>13</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" t="s">
         <v>67</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" t="s">
         <v>69</v>
       </c>
       <c r="G74">
@@ -7060,16 +6979,16 @@
       <c r="B75" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" t="s">
         <v>13</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" t="s">
         <v>9</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" t="s">
         <v>61</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" t="s">
         <v>69</v>
       </c>
       <c r="G75">
@@ -7089,16 +7008,16 @@
       <c r="B76" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" t="s">
         <v>62</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" t="s">
         <v>69</v>
       </c>
       <c r="G76">
@@ -7118,16 +7037,16 @@
       <c r="B77" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" t="s">
         <v>9</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" t="s">
         <v>72</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" t="s">
         <v>69</v>
       </c>
       <c r="G77">
@@ -7147,16 +7066,16 @@
       <c r="B78" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" t="s">
         <v>13</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" t="s">
         <v>73</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" t="s">
         <v>69</v>
       </c>
       <c r="G78">
@@ -7176,16 +7095,16 @@
       <c r="B79" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" t="s">
         <v>16</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" t="s">
         <v>69</v>
       </c>
       <c r="G79">
@@ -7205,16 +7124,16 @@
       <c r="B80" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" t="s">
         <v>16</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" t="s">
         <v>11</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" t="s">
         <v>64</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" t="s">
         <v>69</v>
       </c>
       <c r="G80">
@@ -7234,16 +7153,16 @@
       <c r="B81" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" t="s">
         <v>16</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" t="s">
         <v>66</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" t="s">
         <v>69</v>
       </c>
       <c r="G81">
@@ -7263,16 +7182,16 @@
       <c r="B82" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" t="s">
         <v>16</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" t="s">
         <v>11</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" t="s">
         <v>70</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" t="s">
         <v>69</v>
       </c>
       <c r="G82">
@@ -7292,16 +7211,16 @@
       <c r="B83" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" t="s">
         <v>16</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" t="s">
         <v>11</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" t="s">
         <v>65</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" t="s">
         <v>69</v>
       </c>
       <c r="G83">
@@ -7321,16 +7240,16 @@
       <c r="B84" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" t="s">
         <v>16</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" t="s">
         <v>11</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" t="s">
         <v>71</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" t="s">
         <v>69</v>
       </c>
       <c r="G84">
@@ -7350,16 +7269,16 @@
       <c r="B85" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" t="s">
         <v>16</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" t="s">
         <v>67</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" t="s">
         <v>69</v>
       </c>
       <c r="G85">
@@ -7379,16 +7298,16 @@
       <c r="B86" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" t="s">
         <v>16</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" t="s">
         <v>11</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" t="s">
         <v>61</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" t="s">
         <v>69</v>
       </c>
       <c r="G86">
@@ -7408,16 +7327,16 @@
       <c r="B87" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" t="s">
         <v>16</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" t="s">
         <v>11</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="E87" t="s">
         <v>62</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" t="s">
         <v>69</v>
       </c>
       <c r="G87">
@@ -7437,16 +7356,16 @@
       <c r="B88" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" t="s">
         <v>16</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" t="s">
         <v>11</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" t="s">
         <v>72</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" t="s">
         <v>69</v>
       </c>
       <c r="G88">
@@ -7466,16 +7385,16 @@
       <c r="B89" s="2">
         <v>46159.416666666664</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" t="s">
         <v>16</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" t="s">
         <v>11</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" t="s">
         <v>73</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" t="s">
         <v>69</v>
       </c>
       <c r="G89">
@@ -7495,16 +7414,16 @@
       <c r="B90" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" t="s">
         <v>12</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" t="s">
         <v>63</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" t="s">
         <v>69</v>
       </c>
       <c r="G90">
@@ -7524,16 +7443,16 @@
       <c r="B91" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" t="s">
         <v>12</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" t="s">
         <v>64</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" t="s">
         <v>69</v>
       </c>
       <c r="G91">
@@ -7553,16 +7472,16 @@
       <c r="B92" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" t="s">
         <v>12</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E92" t="s">
         <v>66</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F92" t="s">
         <v>69</v>
       </c>
       <c r="G92">
@@ -7582,16 +7501,16 @@
       <c r="B93" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E93" t="s">
         <v>70</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" t="s">
         <v>69</v>
       </c>
       <c r="G93">
@@ -7611,16 +7530,16 @@
       <c r="B94" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" t="s">
         <v>12</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E94" t="s">
         <v>65</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F94" t="s">
         <v>69</v>
       </c>
       <c r="G94">
@@ -7640,16 +7559,16 @@
       <c r="B95" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" t="s">
         <v>12</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E95" t="s">
         <v>71</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="F95" t="s">
         <v>69</v>
       </c>
       <c r="G95">
@@ -7669,16 +7588,16 @@
       <c r="B96" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" t="s">
         <v>12</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="E96" t="s">
         <v>67</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F96" t="s">
         <v>69</v>
       </c>
       <c r="G96">
@@ -7698,16 +7617,16 @@
       <c r="B97" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="E97" t="s">
         <v>61</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F97" t="s">
         <v>69</v>
       </c>
       <c r="G97">
@@ -7727,16 +7646,16 @@
       <c r="B98" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" t="s">
         <v>12</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E98" t="s">
         <v>62</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F98" t="s">
         <v>69</v>
       </c>
       <c r="G98">
@@ -7756,16 +7675,16 @@
       <c r="B99" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E99" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F99" t="s">
         <v>69</v>
       </c>
       <c r="G99">
@@ -7785,16 +7704,16 @@
       <c r="B100" s="2">
         <v>46163.416666666664</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" t="s">
         <v>12</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" t="s">
         <v>73</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" t="s">
         <v>69</v>
       </c>
       <c r="G100">
@@ -7814,16 +7733,16 @@
       <c r="B101" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" t="s">
         <v>8</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" t="s">
         <v>15</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="E101" t="s">
         <v>63</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" t="s">
         <v>69</v>
       </c>
       <c r="G101">
@@ -7843,16 +7762,16 @@
       <c r="B102" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" t="s">
         <v>8</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" t="s">
         <v>15</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E102" t="s">
         <v>64</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F102" t="s">
         <v>69</v>
       </c>
       <c r="G102">
@@ -7872,16 +7791,16 @@
       <c r="B103" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" t="s">
         <v>8</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" t="s">
         <v>15</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="E103" t="s">
         <v>66</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F103" t="s">
         <v>69</v>
       </c>
       <c r="G103">
@@ -7901,16 +7820,16 @@
       <c r="B104" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" t="s">
         <v>8</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E104" t="s">
         <v>70</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" t="s">
         <v>69</v>
       </c>
       <c r="G104">
@@ -7930,16 +7849,16 @@
       <c r="B105" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" t="s">
         <v>8</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E105" t="s">
         <v>65</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" t="s">
         <v>69</v>
       </c>
       <c r="G105">
@@ -7959,16 +7878,16 @@
       <c r="B106" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" t="s">
         <v>8</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" t="s">
         <v>71</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" t="s">
         <v>69</v>
       </c>
       <c r="G106">
@@ -7988,16 +7907,16 @@
       <c r="B107" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" t="s">
         <v>8</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" t="s">
         <v>15</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E107" t="s">
         <v>67</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F107" t="s">
         <v>69</v>
       </c>
       <c r="G107">
@@ -8017,16 +7936,16 @@
       <c r="B108" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" t="s">
         <v>8</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" t="s">
         <v>15</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" t="s">
         <v>61</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" t="s">
         <v>69</v>
       </c>
       <c r="G108">
@@ -8046,16 +7965,16 @@
       <c r="B109" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" t="s">
         <v>8</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" t="s">
         <v>15</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E109" t="s">
         <v>62</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" t="s">
         <v>69</v>
       </c>
       <c r="G109">
@@ -8075,16 +7994,16 @@
       <c r="B110" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" t="s">
         <v>8</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" t="s">
         <v>72</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" t="s">
         <v>69</v>
       </c>
       <c r="G110">
@@ -8104,16 +8023,16 @@
       <c r="B111" s="2">
         <v>46164.416666666664</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" t="s">
         <v>8</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E111" t="s">
         <v>73</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F111" t="s">
         <v>69</v>
       </c>
       <c r="G111">
@@ -8133,16 +8052,16 @@
       <c r="B112" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" t="s">
         <v>13</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E112" t="s">
         <v>63</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" t="s">
         <v>69</v>
       </c>
       <c r="G112">
@@ -8162,16 +8081,16 @@
       <c r="B113" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" t="s">
         <v>11</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" t="s">
         <v>13</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E113" t="s">
         <v>64</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" t="s">
         <v>69</v>
       </c>
       <c r="G113">
@@ -8191,16 +8110,16 @@
       <c r="B114" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" t="s">
         <v>11</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" t="s">
         <v>13</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E114" t="s">
         <v>66</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" t="s">
         <v>69</v>
       </c>
       <c r="G114">
@@ -8220,16 +8139,16 @@
       <c r="B115" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" t="s">
         <v>11</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" t="s">
         <v>13</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="E115" t="s">
         <v>70</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" t="s">
         <v>69</v>
       </c>
       <c r="G115">
@@ -8249,16 +8168,16 @@
       <c r="B116" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" t="s">
         <v>13</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E116" t="s">
         <v>65</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" t="s">
         <v>69</v>
       </c>
       <c r="G116">
@@ -8278,16 +8197,16 @@
       <c r="B117" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" t="s">
         <v>13</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E117" t="s">
         <v>71</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F117" t="s">
         <v>69</v>
       </c>
       <c r="G117">
@@ -8307,16 +8226,16 @@
       <c r="B118" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" t="s">
         <v>11</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" t="s">
         <v>13</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E118" t="s">
         <v>67</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F118" t="s">
         <v>69</v>
       </c>
       <c r="G118">
@@ -8336,16 +8255,16 @@
       <c r="B119" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" t="s">
         <v>11</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" t="s">
         <v>13</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="E119" t="s">
         <v>61</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F119" t="s">
         <v>69</v>
       </c>
       <c r="G119">
@@ -8365,16 +8284,16 @@
       <c r="B120" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D120" t="s">
         <v>13</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="E120" t="s">
         <v>62</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F120" t="s">
         <v>69</v>
       </c>
       <c r="G120">
@@ -8394,16 +8313,16 @@
       <c r="B121" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" t="s">
         <v>11</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" t="s">
         <v>13</v>
       </c>
-      <c r="E121" s="4" t="s">
+      <c r="E121" t="s">
         <v>72</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="F121" t="s">
         <v>69</v>
       </c>
       <c r="G121">
@@ -8423,16 +8342,16 @@
       <c r="B122" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" t="s">
         <v>13</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" t="s">
         <v>73</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F122" t="s">
         <v>69</v>
       </c>
       <c r="G122">
@@ -8452,16 +8371,16 @@
       <c r="B123" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" t="s">
         <v>19</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D123" t="s">
         <v>22</v>
       </c>
-      <c r="E123" s="4" t="s">
+      <c r="E123" t="s">
         <v>63</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="F123" t="s">
         <v>69</v>
       </c>
       <c r="G123">
@@ -8481,16 +8400,16 @@
       <c r="B124" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" t="s">
         <v>19</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D124" t="s">
         <v>22</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="E124" t="s">
         <v>64</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F124" t="s">
         <v>69</v>
       </c>
       <c r="G124">
@@ -8510,16 +8429,16 @@
       <c r="B125" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" t="s">
         <v>19</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D125" t="s">
         <v>22</v>
       </c>
-      <c r="E125" s="4" t="s">
+      <c r="E125" t="s">
         <v>66</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F125" t="s">
         <v>69</v>
       </c>
       <c r="G125">
@@ -8539,16 +8458,16 @@
       <c r="B126" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" t="s">
         <v>19</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="E126" t="s">
         <v>70</v>
       </c>
-      <c r="F126" s="4" t="s">
+      <c r="F126" t="s">
         <v>69</v>
       </c>
       <c r="G126">
@@ -8568,16 +8487,16 @@
       <c r="B127" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" t="s">
         <v>19</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D127" t="s">
         <v>22</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="E127" t="s">
         <v>65</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="F127" t="s">
         <v>69</v>
       </c>
       <c r="G127">
@@ -8597,16 +8516,16 @@
       <c r="B128" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" t="s">
         <v>19</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D128" t="s">
         <v>22</v>
       </c>
-      <c r="E128" s="4" t="s">
+      <c r="E128" t="s">
         <v>71</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="F128" t="s">
         <v>69</v>
       </c>
       <c r="G128">
@@ -8626,16 +8545,16 @@
       <c r="B129" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" t="s">
         <v>19</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="D129" t="s">
         <v>22</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="E129" t="s">
         <v>67</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="F129" t="s">
         <v>69</v>
       </c>
       <c r="G129">
@@ -8655,16 +8574,16 @@
       <c r="B130" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" t="s">
         <v>19</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" t="s">
         <v>22</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E130" t="s">
         <v>61</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F130" t="s">
         <v>69</v>
       </c>
       <c r="G130">
@@ -8684,16 +8603,16 @@
       <c r="B131" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" t="s">
         <v>19</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D131" t="s">
         <v>22</v>
       </c>
-      <c r="E131" s="4" t="s">
+      <c r="E131" t="s">
         <v>62</v>
       </c>
-      <c r="F131" s="4" t="s">
+      <c r="F131" t="s">
         <v>69</v>
       </c>
       <c r="G131">
@@ -8713,16 +8632,16 @@
       <c r="B132" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" t="s">
         <v>19</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" t="s">
         <v>22</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E132" t="s">
         <v>72</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" t="s">
         <v>69</v>
       </c>
       <c r="G132">
@@ -8742,16 +8661,16 @@
       <c r="B133" s="2">
         <v>46165.416666666664</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" t="s">
         <v>19</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" t="s">
         <v>22</v>
       </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" t="s">
         <v>73</v>
       </c>
-      <c r="F133" s="4" t="s">
+      <c r="F133" t="s">
         <v>69</v>
       </c>
       <c r="G133">
@@ -8771,16 +8690,16 @@
       <c r="B134" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" t="s">
         <v>7</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" t="s">
         <v>14</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E134" t="s">
         <v>63</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="F134" t="s">
         <v>69</v>
       </c>
       <c r="G134">
@@ -8800,16 +8719,16 @@
       <c r="B135" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" t="s">
         <v>7</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" t="s">
         <v>14</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="E135" t="s">
         <v>64</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" t="s">
         <v>69</v>
       </c>
       <c r="G135">
@@ -8829,16 +8748,16 @@
       <c r="B136" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" t="s">
         <v>7</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="D136" t="s">
         <v>14</v>
       </c>
-      <c r="E136" s="4" t="s">
+      <c r="E136" t="s">
         <v>66</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" t="s">
         <v>69</v>
       </c>
       <c r="G136">
@@ -8858,16 +8777,16 @@
       <c r="B137" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" t="s">
         <v>7</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" t="s">
         <v>14</v>
       </c>
-      <c r="E137" s="4" t="s">
+      <c r="E137" t="s">
         <v>70</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="F137" t="s">
         <v>69</v>
       </c>
       <c r="G137">
@@ -8887,16 +8806,16 @@
       <c r="B138" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" t="s">
         <v>7</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="D138" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="4" t="s">
+      <c r="E138" t="s">
         <v>65</v>
       </c>
-      <c r="F138" s="4" t="s">
+      <c r="F138" t="s">
         <v>69</v>
       </c>
       <c r="G138">
@@ -8916,16 +8835,16 @@
       <c r="B139" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" t="s">
         <v>7</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="D139" t="s">
         <v>14</v>
       </c>
-      <c r="E139" s="4" t="s">
+      <c r="E139" t="s">
         <v>71</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="F139" t="s">
         <v>69</v>
       </c>
       <c r="G139">
@@ -8945,16 +8864,16 @@
       <c r="B140" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" t="s">
         <v>7</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="E140" t="s">
         <v>67</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" t="s">
         <v>69</v>
       </c>
       <c r="G140">
@@ -8974,16 +8893,16 @@
       <c r="B141" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" t="s">
         <v>7</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" t="s">
         <v>14</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" t="s">
         <v>61</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="F141" t="s">
         <v>69</v>
       </c>
       <c r="G141">
@@ -9003,16 +8922,16 @@
       <c r="B142" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" t="s">
         <v>7</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D142" t="s">
         <v>14</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" t="s">
         <v>62</v>
       </c>
-      <c r="F142" s="4" t="s">
+      <c r="F142" t="s">
         <v>69</v>
       </c>
       <c r="G142">
@@ -9032,16 +8951,16 @@
       <c r="B143" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" t="s">
         <v>7</v>
       </c>
-      <c r="D143" s="4" t="s">
+      <c r="D143" t="s">
         <v>14</v>
       </c>
-      <c r="E143" s="4" t="s">
+      <c r="E143" t="s">
         <v>72</v>
       </c>
-      <c r="F143" s="4" t="s">
+      <c r="F143" t="s">
         <v>69</v>
       </c>
       <c r="G143">
@@ -9061,16 +8980,16 @@
       <c r="B144" s="2">
         <v>46166.416666666664</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" t="s">
         <v>7</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" t="s">
         <v>14</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E144" t="s">
         <v>73</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="F144" t="s">
         <v>69</v>
       </c>
       <c r="G144">
@@ -9090,16 +9009,16 @@
       <c r="B145" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" t="s">
         <v>6</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" t="s">
         <v>19</v>
       </c>
-      <c r="E145" s="4" t="s">
+      <c r="E145" t="s">
         <v>64</v>
       </c>
-      <c r="F145" s="4" t="s">
+      <c r="F145" t="s">
         <v>69</v>
       </c>
       <c r="G145">
@@ -9119,16 +9038,16 @@
       <c r="B146" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" t="s">
         <v>6</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="D146" t="s">
         <v>19</v>
       </c>
-      <c r="E146" s="4" t="s">
+      <c r="E146" t="s">
         <v>66</v>
       </c>
-      <c r="F146" s="4" t="s">
+      <c r="F146" t="s">
         <v>69</v>
       </c>
       <c r="G146">
@@ -9148,16 +9067,16 @@
       <c r="B147" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" t="s">
         <v>6</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" t="s">
         <v>19</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E147" t="s">
         <v>63</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="F147" t="s">
         <v>69</v>
       </c>
       <c r="G147">
@@ -9177,16 +9096,16 @@
       <c r="B148" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" t="s">
         <v>6</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="D148" t="s">
         <v>19</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="E148" t="s">
         <v>70</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="F148" t="s">
         <v>69</v>
       </c>
       <c r="G148">
@@ -9206,16 +9125,16 @@
       <c r="B149" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" t="s">
         <v>6</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="D149" t="s">
         <v>19</v>
       </c>
-      <c r="E149" s="4" t="s">
+      <c r="E149" t="s">
         <v>65</v>
       </c>
-      <c r="F149" s="4" t="s">
+      <c r="F149" t="s">
         <v>69</v>
       </c>
       <c r="G149">
@@ -9235,16 +9154,16 @@
       <c r="B150" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" t="s">
         <v>6</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="D150" t="s">
         <v>19</v>
       </c>
-      <c r="E150" s="4" t="s">
+      <c r="E150" t="s">
         <v>71</v>
       </c>
-      <c r="F150" s="4" t="s">
+      <c r="F150" t="s">
         <v>69</v>
       </c>
       <c r="G150">
@@ -9264,16 +9183,16 @@
       <c r="B151" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" t="s">
         <v>6</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" t="s">
         <v>19</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E151" t="s">
         <v>67</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="F151" t="s">
         <v>69</v>
       </c>
       <c r="G151">
@@ -9293,16 +9212,16 @@
       <c r="B152" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" t="s">
         <v>6</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="D152" t="s">
         <v>19</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="E152" t="s">
         <v>61</v>
       </c>
-      <c r="F152" s="4" t="s">
+      <c r="F152" t="s">
         <v>69</v>
       </c>
       <c r="G152">
@@ -9322,16 +9241,16 @@
       <c r="B153" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" t="s">
         <v>6</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="D153" t="s">
         <v>19</v>
       </c>
-      <c r="E153" s="4" t="s">
+      <c r="E153" t="s">
         <v>62</v>
       </c>
-      <c r="F153" s="4" t="s">
+      <c r="F153" t="s">
         <v>69</v>
       </c>
       <c r="G153">
@@ -9351,16 +9270,16 @@
       <c r="B154" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" t="s">
         <v>6</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D154" t="s">
         <v>19</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E154" t="s">
         <v>72</v>
       </c>
-      <c r="F154" s="4" t="s">
+      <c r="F154" t="s">
         <v>69</v>
       </c>
       <c r="G154">
@@ -9380,16 +9299,16 @@
       <c r="B155" s="2">
         <v>46171.833333333336</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" t="s">
         <v>6</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" t="s">
         <v>19</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" t="s">
         <v>73</v>
       </c>
-      <c r="F155" s="4" t="s">
+      <c r="F155" t="s">
         <v>69</v>
       </c>
       <c r="G155">
@@ -9409,16 +9328,16 @@
       <c r="B156" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" t="s">
         <v>17</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" t="s">
         <v>18</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="E156" t="s">
         <v>64</v>
       </c>
-      <c r="F156" s="4" t="s">
+      <c r="F156" t="s">
         <v>69</v>
       </c>
       <c r="G156">
@@ -9438,16 +9357,16 @@
       <c r="B157" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" t="s">
         <v>17</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D157" t="s">
         <v>18</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" t="s">
         <v>66</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F157" t="s">
         <v>69</v>
       </c>
       <c r="G157">
@@ -9467,16 +9386,16 @@
       <c r="B158" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" t="s">
         <v>17</v>
       </c>
-      <c r="D158" s="4" t="s">
+      <c r="D158" t="s">
         <v>18</v>
       </c>
-      <c r="E158" s="4" t="s">
+      <c r="E158" t="s">
         <v>63</v>
       </c>
-      <c r="F158" s="4" t="s">
+      <c r="F158" t="s">
         <v>69</v>
       </c>
       <c r="G158">
@@ -9496,16 +9415,16 @@
       <c r="B159" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" t="s">
         <v>17</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="D159" t="s">
         <v>18</v>
       </c>
-      <c r="E159" s="4" t="s">
+      <c r="E159" t="s">
         <v>70</v>
       </c>
-      <c r="F159" s="4" t="s">
+      <c r="F159" t="s">
         <v>69</v>
       </c>
       <c r="G159">
@@ -9525,16 +9444,16 @@
       <c r="B160" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" t="s">
         <v>17</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="D160" t="s">
         <v>18</v>
       </c>
-      <c r="E160" s="4" t="s">
+      <c r="E160" t="s">
         <v>65</v>
       </c>
-      <c r="F160" s="4" t="s">
+      <c r="F160" t="s">
         <v>69</v>
       </c>
       <c r="G160">
@@ -9554,16 +9473,16 @@
       <c r="B161" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" t="s">
         <v>17</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="D161" t="s">
         <v>18</v>
       </c>
-      <c r="E161" s="4" t="s">
+      <c r="E161" t="s">
         <v>71</v>
       </c>
-      <c r="F161" s="4" t="s">
+      <c r="F161" t="s">
         <v>69</v>
       </c>
       <c r="G161">
@@ -9583,16 +9502,16 @@
       <c r="B162" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" t="s">
         <v>17</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="D162" t="s">
         <v>18</v>
       </c>
-      <c r="E162" s="4" t="s">
+      <c r="E162" t="s">
         <v>67</v>
       </c>
-      <c r="F162" s="4" t="s">
+      <c r="F162" t="s">
         <v>69</v>
       </c>
       <c r="G162">
@@ -9612,16 +9531,16 @@
       <c r="B163" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" t="s">
         <v>17</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="D163" t="s">
         <v>18</v>
       </c>
-      <c r="E163" s="4" t="s">
+      <c r="E163" t="s">
         <v>61</v>
       </c>
-      <c r="F163" s="4" t="s">
+      <c r="F163" t="s">
         <v>69</v>
       </c>
       <c r="G163">
@@ -9641,16 +9560,16 @@
       <c r="B164" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" t="s">
         <v>17</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="D164" t="s">
         <v>18</v>
       </c>
-      <c r="E164" s="4" t="s">
+      <c r="E164" t="s">
         <v>62</v>
       </c>
-      <c r="F164" s="4" t="s">
+      <c r="F164" t="s">
         <v>69</v>
       </c>
       <c r="G164">
@@ -9670,16 +9589,16 @@
       <c r="B165" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" t="s">
         <v>17</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" t="s">
         <v>18</v>
       </c>
-      <c r="E165" s="4" t="s">
+      <c r="E165" t="s">
         <v>72</v>
       </c>
-      <c r="F165" s="4" t="s">
+      <c r="F165" t="s">
         <v>69</v>
       </c>
       <c r="G165">
@@ -9699,16 +9618,16 @@
       <c r="B166" s="2">
         <v>46172.625</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" t="s">
         <v>17</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" t="s">
         <v>18</v>
       </c>
-      <c r="E166" s="4" t="s">
+      <c r="E166" t="s">
         <v>73</v>
       </c>
-      <c r="F166" s="4" t="s">
+      <c r="F166" t="s">
         <v>69</v>
       </c>
       <c r="G166">
@@ -9728,16 +9647,16 @@
       <c r="B167" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" t="s">
         <v>5</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="D167" t="s">
         <v>8</v>
       </c>
-      <c r="E167" s="4" t="s">
+      <c r="E167" t="s">
         <v>64</v>
       </c>
-      <c r="F167" s="4" t="s">
+      <c r="F167" t="s">
         <v>69</v>
       </c>
       <c r="G167">
@@ -9757,16 +9676,16 @@
       <c r="B168" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" t="s">
         <v>5</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="D168" t="s">
         <v>8</v>
       </c>
-      <c r="E168" s="4" t="s">
+      <c r="E168" t="s">
         <v>66</v>
       </c>
-      <c r="F168" s="4" t="s">
+      <c r="F168" t="s">
         <v>69</v>
       </c>
       <c r="G168">
@@ -9786,16 +9705,16 @@
       <c r="B169" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" t="s">
         <v>5</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="D169" t="s">
         <v>8</v>
       </c>
-      <c r="E169" s="4" t="s">
+      <c r="E169" t="s">
         <v>63</v>
       </c>
-      <c r="F169" s="4" t="s">
+      <c r="F169" t="s">
         <v>69</v>
       </c>
       <c r="G169">
@@ -9815,16 +9734,16 @@
       <c r="B170" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" t="s">
         <v>5</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="D170" t="s">
         <v>8</v>
       </c>
-      <c r="E170" s="4" t="s">
+      <c r="E170" t="s">
         <v>70</v>
       </c>
-      <c r="F170" s="4" t="s">
+      <c r="F170" t="s">
         <v>69</v>
       </c>
       <c r="G170">
@@ -9844,16 +9763,16 @@
       <c r="B171" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" t="s">
         <v>5</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="D171" t="s">
         <v>8</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="E171" t="s">
         <v>65</v>
       </c>
-      <c r="F171" s="4" t="s">
+      <c r="F171" t="s">
         <v>69</v>
       </c>
       <c r="G171">
@@ -9873,16 +9792,16 @@
       <c r="B172" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" t="s">
         <v>5</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="D172" t="s">
         <v>8</v>
       </c>
-      <c r="E172" s="4" t="s">
+      <c r="E172" t="s">
         <v>71</v>
       </c>
-      <c r="F172" s="4" t="s">
+      <c r="F172" t="s">
         <v>69</v>
       </c>
       <c r="G172">
@@ -9902,16 +9821,16 @@
       <c r="B173" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" t="s">
         <v>5</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="D173" t="s">
         <v>8</v>
       </c>
-      <c r="E173" s="4" t="s">
+      <c r="E173" t="s">
         <v>67</v>
       </c>
-      <c r="F173" s="4" t="s">
+      <c r="F173" t="s">
         <v>69</v>
       </c>
       <c r="G173">
@@ -9931,16 +9850,16 @@
       <c r="B174" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" t="s">
         <v>5</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="D174" t="s">
         <v>8</v>
       </c>
-      <c r="E174" s="4" t="s">
+      <c r="E174" t="s">
         <v>61</v>
       </c>
-      <c r="F174" s="4" t="s">
+      <c r="F174" t="s">
         <v>69</v>
       </c>
       <c r="G174">
@@ -9960,16 +9879,16 @@
       <c r="B175" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" t="s">
         <v>5</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" t="s">
         <v>8</v>
       </c>
-      <c r="E175" s="4" t="s">
+      <c r="E175" t="s">
         <v>62</v>
       </c>
-      <c r="F175" s="4" t="s">
+      <c r="F175" t="s">
         <v>69</v>
       </c>
       <c r="G175">
@@ -9989,16 +9908,16 @@
       <c r="B176" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" t="s">
         <v>5</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" t="s">
         <v>8</v>
       </c>
-      <c r="E176" s="4" t="s">
+      <c r="E176" t="s">
         <v>72</v>
       </c>
-      <c r="F176" s="4" t="s">
+      <c r="F176" t="s">
         <v>69</v>
       </c>
       <c r="G176">
@@ -10018,16 +9937,16 @@
       <c r="B177" s="2">
         <v>46172.729166666664</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" t="s">
         <v>5</v>
       </c>
-      <c r="D177" s="4" t="s">
+      <c r="D177" t="s">
         <v>8</v>
       </c>
-      <c r="E177" s="4" t="s">
+      <c r="E177" t="s">
         <v>73</v>
       </c>
-      <c r="F177" s="4" t="s">
+      <c r="F177" t="s">
         <v>69</v>
       </c>
       <c r="G177">
@@ -10047,16 +9966,16 @@
       <c r="B178" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" t="s">
         <v>15</v>
       </c>
-      <c r="D178" s="4" t="s">
+      <c r="D178" t="s">
         <v>10</v>
       </c>
-      <c r="E178" s="4" t="s">
+      <c r="E178" t="s">
         <v>64</v>
       </c>
-      <c r="F178" s="4" t="s">
+      <c r="F178" t="s">
         <v>69</v>
       </c>
       <c r="G178">
@@ -10076,16 +9995,16 @@
       <c r="B179" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" t="s">
         <v>15</v>
       </c>
-      <c r="D179" s="4" t="s">
+      <c r="D179" t="s">
         <v>10</v>
       </c>
-      <c r="E179" s="4" t="s">
+      <c r="E179" t="s">
         <v>66</v>
       </c>
-      <c r="F179" s="4" t="s">
+      <c r="F179" t="s">
         <v>69</v>
       </c>
       <c r="G179">
@@ -10105,16 +10024,16 @@
       <c r="B180" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" t="s">
         <v>15</v>
       </c>
-      <c r="D180" s="4" t="s">
+      <c r="D180" t="s">
         <v>10</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E180" t="s">
         <v>63</v>
       </c>
-      <c r="F180" s="4" t="s">
+      <c r="F180" t="s">
         <v>69</v>
       </c>
       <c r="G180">
@@ -10134,16 +10053,16 @@
       <c r="B181" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" t="s">
         <v>15</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" t="s">
         <v>10</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E181" t="s">
         <v>70</v>
       </c>
-      <c r="F181" s="4" t="s">
+      <c r="F181" t="s">
         <v>69</v>
       </c>
       <c r="G181">
@@ -10163,16 +10082,16 @@
       <c r="B182" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" t="s">
         <v>15</v>
       </c>
-      <c r="D182" s="4" t="s">
+      <c r="D182" t="s">
         <v>10</v>
       </c>
-      <c r="E182" s="4" t="s">
+      <c r="E182" t="s">
         <v>65</v>
       </c>
-      <c r="F182" s="4" t="s">
+      <c r="F182" t="s">
         <v>69</v>
       </c>
       <c r="G182">
@@ -10192,16 +10111,16 @@
       <c r="B183" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" t="s">
         <v>15</v>
       </c>
-      <c r="D183" s="4" t="s">
+      <c r="D183" t="s">
         <v>10</v>
       </c>
-      <c r="E183" s="4" t="s">
+      <c r="E183" t="s">
         <v>71</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="F183" t="s">
         <v>69</v>
       </c>
       <c r="G183">
@@ -10221,16 +10140,16 @@
       <c r="B184" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" t="s">
         <v>15</v>
       </c>
-      <c r="D184" s="4" t="s">
+      <c r="D184" t="s">
         <v>10</v>
       </c>
-      <c r="E184" s="4" t="s">
+      <c r="E184" t="s">
         <v>67</v>
       </c>
-      <c r="F184" s="4" t="s">
+      <c r="F184" t="s">
         <v>69</v>
       </c>
       <c r="G184">
@@ -10250,16 +10169,16 @@
       <c r="B185" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" t="s">
         <v>15</v>
       </c>
-      <c r="D185" s="4" t="s">
+      <c r="D185" t="s">
         <v>10</v>
       </c>
-      <c r="E185" s="4" t="s">
+      <c r="E185" t="s">
         <v>61</v>
       </c>
-      <c r="F185" s="4" t="s">
+      <c r="F185" t="s">
         <v>69</v>
       </c>
       <c r="G185">
@@ -10279,16 +10198,16 @@
       <c r="B186" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" t="s">
         <v>15</v>
       </c>
-      <c r="D186" s="4" t="s">
+      <c r="D186" t="s">
         <v>10</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E186" t="s">
         <v>62</v>
       </c>
-      <c r="F186" s="4" t="s">
+      <c r="F186" t="s">
         <v>69</v>
       </c>
       <c r="G186">
@@ -10308,16 +10227,16 @@
       <c r="B187" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C187" t="s">
         <v>15</v>
       </c>
-      <c r="D187" s="4" t="s">
+      <c r="D187" t="s">
         <v>10</v>
       </c>
-      <c r="E187" s="4" t="s">
+      <c r="E187" t="s">
         <v>72</v>
       </c>
-      <c r="F187" s="4" t="s">
+      <c r="F187" t="s">
         <v>69</v>
       </c>
       <c r="G187">
@@ -10337,16 +10256,16 @@
       <c r="B188" s="2">
         <v>46172.815972222219</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" t="s">
         <v>15</v>
       </c>
-      <c r="D188" s="4" t="s">
+      <c r="D188" t="s">
         <v>10</v>
       </c>
-      <c r="E188" s="4" t="s">
+      <c r="E188" t="s">
         <v>73</v>
       </c>
-      <c r="F188" s="4" t="s">
+      <c r="F188" t="s">
         <v>69</v>
       </c>
       <c r="G188">
@@ -10366,16 +10285,16 @@
       <c r="B189" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C189" s="4" t="s">
+      <c r="C189" t="s">
         <v>9</v>
       </c>
-      <c r="D189" s="4" t="s">
+      <c r="D189" t="s">
         <v>11</v>
       </c>
-      <c r="E189" s="4" t="s">
+      <c r="E189" t="s">
         <v>64</v>
       </c>
-      <c r="F189" s="4" t="s">
+      <c r="F189" t="s">
         <v>69</v>
       </c>
       <c r="G189">
@@ -10395,16 +10314,16 @@
       <c r="B190" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" t="s">
         <v>9</v>
       </c>
-      <c r="D190" s="4" t="s">
+      <c r="D190" t="s">
         <v>11</v>
       </c>
-      <c r="E190" s="4" t="s">
+      <c r="E190" t="s">
         <v>66</v>
       </c>
-      <c r="F190" s="4" t="s">
+      <c r="F190" t="s">
         <v>69</v>
       </c>
       <c r="G190">
@@ -10424,16 +10343,16 @@
       <c r="B191" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" t="s">
         <v>9</v>
       </c>
-      <c r="D191" s="4" t="s">
+      <c r="D191" t="s">
         <v>11</v>
       </c>
-      <c r="E191" s="4" t="s">
+      <c r="E191" t="s">
         <v>63</v>
       </c>
-      <c r="F191" s="4" t="s">
+      <c r="F191" t="s">
         <v>69</v>
       </c>
       <c r="G191">
@@ -10453,16 +10372,16 @@
       <c r="B192" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C192" t="s">
         <v>9</v>
       </c>
-      <c r="D192" s="4" t="s">
+      <c r="D192" t="s">
         <v>11</v>
       </c>
-      <c r="E192" s="4" t="s">
+      <c r="E192" t="s">
         <v>70</v>
       </c>
-      <c r="F192" s="4" t="s">
+      <c r="F192" t="s">
         <v>69</v>
       </c>
       <c r="G192">
@@ -10482,16 +10401,16 @@
       <c r="B193" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C193" t="s">
         <v>9</v>
       </c>
-      <c r="D193" s="4" t="s">
+      <c r="D193" t="s">
         <v>11</v>
       </c>
-      <c r="E193" s="4" t="s">
+      <c r="E193" t="s">
         <v>65</v>
       </c>
-      <c r="F193" s="4" t="s">
+      <c r="F193" t="s">
         <v>69</v>
       </c>
       <c r="G193">
@@ -10511,16 +10430,16 @@
       <c r="B194" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" t="s">
         <v>9</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D194" t="s">
         <v>11</v>
       </c>
-      <c r="E194" s="4" t="s">
+      <c r="E194" t="s">
         <v>71</v>
       </c>
-      <c r="F194" s="4" t="s">
+      <c r="F194" t="s">
         <v>69</v>
       </c>
       <c r="G194">
@@ -10540,16 +10459,16 @@
       <c r="B195" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" t="s">
         <v>9</v>
       </c>
-      <c r="D195" s="4" t="s">
+      <c r="D195" t="s">
         <v>11</v>
       </c>
-      <c r="E195" s="4" t="s">
+      <c r="E195" t="s">
         <v>67</v>
       </c>
-      <c r="F195" s="4" t="s">
+      <c r="F195" t="s">
         <v>69</v>
       </c>
       <c r="G195">
@@ -10569,16 +10488,16 @@
       <c r="B196" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" t="s">
         <v>9</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D196" t="s">
         <v>11</v>
       </c>
-      <c r="E196" s="4" t="s">
+      <c r="E196" t="s">
         <v>61</v>
       </c>
-      <c r="F196" s="4" t="s">
+      <c r="F196" t="s">
         <v>69</v>
       </c>
       <c r="G196">
@@ -10598,16 +10517,16 @@
       <c r="B197" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" t="s">
         <v>9</v>
       </c>
-      <c r="D197" s="4" t="s">
+      <c r="D197" t="s">
         <v>11</v>
       </c>
-      <c r="E197" s="4" t="s">
+      <c r="E197" t="s">
         <v>62</v>
       </c>
-      <c r="F197" s="4" t="s">
+      <c r="F197" t="s">
         <v>69</v>
       </c>
       <c r="G197">
@@ -10627,16 +10546,16 @@
       <c r="B198" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" t="s">
         <v>9</v>
       </c>
-      <c r="D198" s="4" t="s">
+      <c r="D198" t="s">
         <v>11</v>
       </c>
-      <c r="E198" s="4" t="s">
+      <c r="E198" t="s">
         <v>72</v>
       </c>
-      <c r="F198" s="4" t="s">
+      <c r="F198" t="s">
         <v>69</v>
       </c>
       <c r="G198">
@@ -10656,16 +10575,16 @@
       <c r="B199" s="2">
         <v>46173.583333333336</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" t="s">
         <v>9</v>
       </c>
-      <c r="D199" s="4" t="s">
+      <c r="D199" t="s">
         <v>11</v>
       </c>
-      <c r="E199" s="4" t="s">
+      <c r="E199" t="s">
         <v>73</v>
       </c>
-      <c r="F199" s="4" t="s">
+      <c r="F199" t="s">
         <v>69</v>
       </c>
       <c r="G199">
@@ -10685,16 +10604,16 @@
       <c r="B200" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="4" t="s">
+      <c r="D200" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="4" t="s">
+      <c r="E200" t="s">
         <v>64</v>
       </c>
-      <c r="F200" s="4" t="s">
+      <c r="F200" t="s">
         <v>69</v>
       </c>
       <c r="G200">
@@ -10714,16 +10633,16 @@
       <c r="B201" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="D201" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="4" t="s">
+      <c r="E201" t="s">
         <v>66</v>
       </c>
-      <c r="F201" s="4" t="s">
+      <c r="F201" t="s">
         <v>69</v>
       </c>
       <c r="G201">
@@ -10743,16 +10662,16 @@
       <c r="B202" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="4" t="s">
+      <c r="D202" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="4" t="s">
+      <c r="E202" t="s">
         <v>63</v>
       </c>
-      <c r="F202" s="4" t="s">
+      <c r="F202" t="s">
         <v>69</v>
       </c>
       <c r="G202">
@@ -10772,16 +10691,16 @@
       <c r="B203" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="4" t="s">
+      <c r="D203" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="4" t="s">
+      <c r="E203" t="s">
         <v>70</v>
       </c>
-      <c r="F203" s="4" t="s">
+      <c r="F203" t="s">
         <v>69</v>
       </c>
       <c r="G203">
@@ -10801,16 +10720,16 @@
       <c r="B204" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="4" t="s">
+      <c r="D204" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="4" t="s">
+      <c r="E204" t="s">
         <v>65</v>
       </c>
-      <c r="F204" s="4" t="s">
+      <c r="F204" t="s">
         <v>69</v>
       </c>
       <c r="G204">
@@ -10830,16 +10749,16 @@
       <c r="B205" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="4" t="s">
+      <c r="D205" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="4" t="s">
+      <c r="E205" t="s">
         <v>71</v>
       </c>
-      <c r="F205" s="4" t="s">
+      <c r="F205" t="s">
         <v>69</v>
       </c>
       <c r="G205">
@@ -10859,16 +10778,16 @@
       <c r="B206" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="4" t="s">
+      <c r="D206" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="4" t="s">
+      <c r="E206" t="s">
         <v>67</v>
       </c>
-      <c r="F206" s="4" t="s">
+      <c r="F206" t="s">
         <v>69</v>
       </c>
       <c r="G206">
@@ -10888,16 +10807,16 @@
       <c r="B207" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="4" t="s">
+      <c r="D207" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="4" t="s">
+      <c r="E207" t="s">
         <v>61</v>
       </c>
-      <c r="F207" s="4" t="s">
+      <c r="F207" t="s">
         <v>69</v>
       </c>
       <c r="G207">
@@ -10917,16 +10836,16 @@
       <c r="B208" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="4" t="s">
+      <c r="D208" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="4" t="s">
+      <c r="E208" t="s">
         <v>62</v>
       </c>
-      <c r="F208" s="4" t="s">
+      <c r="F208" t="s">
         <v>69</v>
       </c>
       <c r="G208">
@@ -10946,16 +10865,16 @@
       <c r="B209" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="4" t="s">
+      <c r="D209" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="4" t="s">
+      <c r="E209" t="s">
         <v>72</v>
       </c>
-      <c r="F209" s="4" t="s">
+      <c r="F209" t="s">
         <v>69</v>
       </c>
       <c r="G209">
@@ -10975,16 +10894,16 @@
       <c r="B210" s="2">
         <v>46173.670138888891</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="4" t="s">
+      <c r="D210" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="4" t="s">
+      <c r="E210" t="s">
         <v>73</v>
       </c>
-      <c r="F210" s="4" t="s">
+      <c r="F210" t="s">
         <v>69</v>
       </c>
       <c r="G210">
@@ -11004,16 +10923,16 @@
       <c r="B211" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" t="s">
         <v>16</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" t="s">
         <v>13</v>
       </c>
-      <c r="E211" s="4" t="s">
+      <c r="E211" t="s">
         <v>64</v>
       </c>
-      <c r="F211" s="4" t="s">
+      <c r="F211" t="s">
         <v>69</v>
       </c>
       <c r="G211">
@@ -11033,16 +10952,16 @@
       <c r="B212" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" t="s">
         <v>16</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" t="s">
         <v>13</v>
       </c>
-      <c r="E212" s="4" t="s">
+      <c r="E212" t="s">
         <v>66</v>
       </c>
-      <c r="F212" s="4" t="s">
+      <c r="F212" t="s">
         <v>69</v>
       </c>
       <c r="G212">
@@ -11062,16 +10981,16 @@
       <c r="B213" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" t="s">
         <v>16</v>
       </c>
-      <c r="D213" s="4" t="s">
+      <c r="D213" t="s">
         <v>13</v>
       </c>
-      <c r="E213" s="4" t="s">
+      <c r="E213" t="s">
         <v>63</v>
       </c>
-      <c r="F213" s="4" t="s">
+      <c r="F213" t="s">
         <v>69</v>
       </c>
       <c r="G213">
@@ -11091,16 +11010,16 @@
       <c r="B214" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" t="s">
         <v>16</v>
       </c>
-      <c r="D214" s="4" t="s">
+      <c r="D214" t="s">
         <v>13</v>
       </c>
-      <c r="E214" s="4" t="s">
+      <c r="E214" t="s">
         <v>70</v>
       </c>
-      <c r="F214" s="4" t="s">
+      <c r="F214" t="s">
         <v>69</v>
       </c>
       <c r="G214">
@@ -11120,16 +11039,16 @@
       <c r="B215" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" t="s">
         <v>16</v>
       </c>
-      <c r="D215" s="4" t="s">
+      <c r="D215" t="s">
         <v>13</v>
       </c>
-      <c r="E215" s="4" t="s">
+      <c r="E215" t="s">
         <v>65</v>
       </c>
-      <c r="F215" s="4" t="s">
+      <c r="F215" t="s">
         <v>69</v>
       </c>
       <c r="G215">
@@ -11149,16 +11068,16 @@
       <c r="B216" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" t="s">
         <v>16</v>
       </c>
-      <c r="D216" s="4" t="s">
+      <c r="D216" t="s">
         <v>13</v>
       </c>
-      <c r="E216" s="4" t="s">
+      <c r="E216" t="s">
         <v>71</v>
       </c>
-      <c r="F216" s="4" t="s">
+      <c r="F216" t="s">
         <v>69</v>
       </c>
       <c r="G216">
@@ -11178,16 +11097,16 @@
       <c r="B217" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C217" t="s">
         <v>16</v>
       </c>
-      <c r="D217" s="4" t="s">
+      <c r="D217" t="s">
         <v>13</v>
       </c>
-      <c r="E217" s="4" t="s">
+      <c r="E217" t="s">
         <v>67</v>
       </c>
-      <c r="F217" s="4" t="s">
+      <c r="F217" t="s">
         <v>69</v>
       </c>
       <c r="G217">
@@ -11207,16 +11126,16 @@
       <c r="B218" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C218" t="s">
         <v>16</v>
       </c>
-      <c r="D218" s="4" t="s">
+      <c r="D218" t="s">
         <v>13</v>
       </c>
-      <c r="E218" s="4" t="s">
+      <c r="E218" t="s">
         <v>61</v>
       </c>
-      <c r="F218" s="4" t="s">
+      <c r="F218" t="s">
         <v>69</v>
       </c>
       <c r="G218">
@@ -11236,16 +11155,16 @@
       <c r="B219" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="C219" t="s">
         <v>16</v>
       </c>
-      <c r="D219" s="4" t="s">
+      <c r="D219" t="s">
         <v>13</v>
       </c>
-      <c r="E219" s="4" t="s">
+      <c r="E219" t="s">
         <v>62</v>
       </c>
-      <c r="F219" s="4" t="s">
+      <c r="F219" t="s">
         <v>69</v>
       </c>
       <c r="G219">
@@ -11265,16 +11184,16 @@
       <c r="B220" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" t="s">
         <v>16</v>
       </c>
-      <c r="D220" s="4" t="s">
+      <c r="D220" t="s">
         <v>13</v>
       </c>
-      <c r="E220" s="4" t="s">
+      <c r="E220" t="s">
         <v>72</v>
       </c>
-      <c r="F220" s="4" t="s">
+      <c r="F220" t="s">
         <v>69</v>
       </c>
       <c r="G220">
@@ -11294,16 +11213,16 @@
       <c r="B221" s="2">
         <v>46173.760416666664</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" t="s">
         <v>16</v>
       </c>
-      <c r="D221" s="4" t="s">
+      <c r="D221" t="s">
         <v>13</v>
       </c>
-      <c r="E221" s="4" t="s">
+      <c r="E221" t="s">
         <v>73</v>
       </c>
-      <c r="F221" s="4" t="s">
+      <c r="F221" t="s">
         <v>69</v>
       </c>
       <c r="G221">
